--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Banking & PSU Debt Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Banking & PSU Debt Fund.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\OPERAT\Factsheet 2013-14\January 2025\ISIN Port 310125_new\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\OPERAT\Factsheet 2013-14\May 2025\ISIN Portfolios 310525\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="222">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -27,7 +27,7 @@
     <t>ICICI Prudential Banking &amp; PSU Debt Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -75,79 +75,115 @@
     <t>SOV</t>
   </si>
   <si>
+    <t>IN0020240035</t>
+  </si>
+  <si>
     <t>IN0020200120</t>
   </si>
   <si>
     <t>IN0020210137</t>
   </si>
   <si>
+    <t>IN0020240126</t>
+  </si>
+  <si>
+    <t>State Government of Maharashtra</t>
+  </si>
+  <si>
+    <t>IN2220240427</t>
+  </si>
+  <si>
+    <t>IN0020250018</t>
+  </si>
+  <si>
+    <t>IN2220240435</t>
+  </si>
+  <si>
+    <t>State Government of Chhattisgarh</t>
+  </si>
+  <si>
+    <t>IN3520240083</t>
+  </si>
+  <si>
+    <t>State Government of Karnataka</t>
+  </si>
+  <si>
+    <t>IN1920240257</t>
+  </si>
+  <si>
+    <t>State Government of West Bengal</t>
+  </si>
+  <si>
+    <t>IN3420240241</t>
+  </si>
+  <si>
     <t>IN0020240134</t>
   </si>
   <si>
-    <t>IN0020230085</t>
-  </si>
-  <si>
-    <t>IN0020240126</t>
-  </si>
-  <si>
-    <t>State Government of Rajasthan</t>
-  </si>
-  <si>
-    <t>IN2920140240</t>
+    <t>^</t>
   </si>
   <si>
     <t>Non-Convertible debentures / Bonds</t>
   </si>
   <si>
+    <t>NABARD</t>
+  </si>
+  <si>
+    <t>INE261F08DX0</t>
+  </si>
+  <si>
+    <t>CRISIL AAA</t>
+  </si>
+  <si>
+    <t>HDFC Bank Ltd. **</t>
+  </si>
+  <si>
+    <t>INE040A08AF2</t>
+  </si>
+  <si>
+    <t>State Bank of India ( Tier II Bond under Basel III ) **</t>
+  </si>
+  <si>
+    <t>INE062A08256</t>
+  </si>
+  <si>
+    <t>LIC Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE115A07QV7</t>
+  </si>
+  <si>
+    <t>INE115A07RF8</t>
+  </si>
+  <si>
+    <t>NABARD **</t>
+  </si>
+  <si>
+    <t>INE261F08EM1</t>
+  </si>
+  <si>
+    <t>ICRA AAA</t>
+  </si>
+  <si>
+    <t>Mahanagar Telephone Nigam Ltd. **</t>
+  </si>
+  <si>
+    <t>INE153A08170</t>
+  </si>
+  <si>
+    <t>FITCH AAA(CE)</t>
+  </si>
+  <si>
     <t>Small Industries Development Bank Of India. **</t>
   </si>
   <si>
-    <t>INE556F08KA6</t>
-  </si>
-  <si>
-    <t>ICRA AAA</t>
-  </si>
-  <si>
-    <t>NABARD</t>
-  </si>
-  <si>
-    <t>INE261F08DX0</t>
-  </si>
-  <si>
-    <t>CRISIL AAA</t>
-  </si>
-  <si>
-    <t>HDFC Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE040A08AF2</t>
-  </si>
-  <si>
-    <t>State Bank of India ( Tier II Bond under Basel III ) **</t>
-  </si>
-  <si>
-    <t>INE062A08256</t>
-  </si>
-  <si>
-    <t>NABARD **</t>
-  </si>
-  <si>
-    <t>INE261F08DW2</t>
-  </si>
-  <si>
-    <t>LIC Housing Finance Ltd.</t>
-  </si>
-  <si>
-    <t>INE115A07QV7</t>
-  </si>
-  <si>
-    <t>Mahanagar Telephone Nigam Ltd.</t>
-  </si>
-  <si>
-    <t>INE153A08170</t>
-  </si>
-  <si>
-    <t>FITCH AAA(CE)</t>
+    <t>INE556F08KQ2</t>
+  </si>
+  <si>
+    <t>Rural Electrification Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE020B08EI8</t>
   </si>
   <si>
     <t>Bharat Petroleum Corporation Ltd. **</t>
@@ -159,7 +195,7 @@
     <t>Rural Electrification Corporation Ltd. **</t>
   </si>
   <si>
-    <t>INE020B08EI8</t>
+    <t>INE020B08EL2</t>
   </si>
   <si>
     <t>Power Finance Corporation Ltd. **</t>
@@ -186,43 +222,220 @@
     <t>INE031A08871</t>
   </si>
   <si>
-    <t>INE261F08EM1</t>
-  </si>
-  <si>
     <t>INE020B08ED9</t>
   </si>
   <si>
-    <t>INE020B08EL2</t>
+    <t>INE556F08KU4</t>
+  </si>
+  <si>
+    <t>INE261F08EI9</t>
+  </si>
+  <si>
+    <t>INE556F08KI9</t>
   </si>
   <si>
     <t>INE040A08666</t>
   </si>
   <si>
-    <t>INE134E08MN4</t>
+    <t>INE261F08DV4</t>
+  </si>
+  <si>
+    <t>Power Finance Corporation Ltd.</t>
+  </si>
+  <si>
+    <t>INE134E08LP1</t>
+  </si>
+  <si>
+    <t>INE040A08AI6</t>
+  </si>
+  <si>
+    <t>INE556F08KN9</t>
+  </si>
+  <si>
+    <t>INE556F08KH1</t>
+  </si>
+  <si>
+    <t>INE062A08264</t>
+  </si>
+  <si>
+    <t>DME Development Ltd. **</t>
+  </si>
+  <si>
+    <t>INE0J7Q07249</t>
+  </si>
+  <si>
+    <t>INE261F08EK5</t>
+  </si>
+  <si>
+    <t>INE134E08LK2</t>
+  </si>
+  <si>
+    <t>INE556F08KT6</t>
+  </si>
+  <si>
+    <t>INE556F08KK5</t>
+  </si>
+  <si>
+    <t>INE153A08089</t>
+  </si>
+  <si>
+    <t>BWR AA+(CE)</t>
+  </si>
+  <si>
+    <t>INE134E08MT1</t>
+  </si>
+  <si>
+    <t>INE020B08ES7</t>
+  </si>
+  <si>
+    <t>INE020B08EM0</t>
+  </si>
+  <si>
+    <t>INE020B08EF4</t>
+  </si>
+  <si>
+    <t>Citicorp Finance (India) Ltd. **</t>
+  </si>
+  <si>
+    <t>INE915D08CY6</t>
+  </si>
+  <si>
+    <t>INE134E08MJ2</t>
+  </si>
+  <si>
+    <t>INE134E08JP5</t>
+  </si>
+  <si>
+    <t>Axis Bank Ltd. **</t>
+  </si>
+  <si>
+    <t>INE238A08450</t>
+  </si>
+  <si>
+    <t>Bharat Sanchar Nigam Ltd. **</t>
+  </si>
+  <si>
+    <t>INE103D08054</t>
+  </si>
+  <si>
+    <t>CRISIL AAA(CE)</t>
+  </si>
+  <si>
+    <t>INE115A07RB7</t>
+  </si>
+  <si>
+    <t>INE020B08EA5</t>
   </si>
   <si>
     <t>Small Industries Development Bank Of India.</t>
   </si>
   <si>
-    <t>INE556F08KI9</t>
-  </si>
-  <si>
-    <t>INE020B08EF4</t>
-  </si>
-  <si>
-    <t>INE261F08DV4</t>
-  </si>
-  <si>
-    <t>Axis Bank Ltd. **</t>
+    <t>INE556F08KS8</t>
+  </si>
+  <si>
+    <t>INE134E08NL6</t>
+  </si>
+  <si>
+    <t>INE556F08KM1</t>
+  </si>
+  <si>
+    <t>INE261F08EF5</t>
+  </si>
+  <si>
+    <t>INE040A08AA3</t>
+  </si>
+  <si>
+    <t>INE040A08542</t>
+  </si>
+  <si>
+    <t>INE556F08KJ7</t>
+  </si>
+  <si>
+    <t>Indian Railway Finance Corporation Ltd. **</t>
+  </si>
+  <si>
+    <t>INE053F08304</t>
+  </si>
+  <si>
+    <t>INE031A08855</t>
+  </si>
+  <si>
+    <t>INE020B08ET5</t>
+  </si>
+  <si>
+    <t>INE020B08AH8</t>
+  </si>
+  <si>
+    <t>Kotak Mahindra Bank Ltd. **</t>
+  </si>
+  <si>
+    <t>INE237A08940</t>
+  </si>
+  <si>
+    <t>INE020B08FA2</t>
   </si>
   <si>
     <t>INE238A08468</t>
   </si>
   <si>
-    <t>DME Development Ltd. **</t>
-  </si>
-  <si>
-    <t>INE0J7Q07249</t>
+    <t>INE0J7Q07017</t>
+  </si>
+  <si>
+    <t>INE0J7Q07108</t>
+  </si>
+  <si>
+    <t>INE0J7Q07074</t>
+  </si>
+  <si>
+    <t>INE0J7Q07090</t>
+  </si>
+  <si>
+    <t>INE0J7Q07082</t>
+  </si>
+  <si>
+    <t>INE0J7Q07058</t>
+  </si>
+  <si>
+    <t>INE0J7Q07025</t>
+  </si>
+  <si>
+    <t>INE0J7Q07033</t>
+  </si>
+  <si>
+    <t>INE0J7Q07066</t>
+  </si>
+  <si>
+    <t>INE0J7Q07041</t>
+  </si>
+  <si>
+    <t>INE134E08LX5</t>
+  </si>
+  <si>
+    <t>INE040A08955</t>
+  </si>
+  <si>
+    <t>INE261F08EA6</t>
+  </si>
+  <si>
+    <t>HDFC Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE040A08807</t>
+  </si>
+  <si>
+    <t>INE040A08914</t>
+  </si>
+  <si>
+    <t>INE040A08435</t>
+  </si>
+  <si>
+    <t>INE040A08773</t>
+  </si>
+  <si>
+    <t>INE134E08IX1</t>
+  </si>
+  <si>
+    <t>INE040A08757</t>
   </si>
   <si>
     <t>Tata Capital Housing Finance Ltd. **</t>
@@ -231,178 +444,31 @@
     <t>INE033L07IK9</t>
   </si>
   <si>
-    <t>INE556F08KH1</t>
-  </si>
-  <si>
-    <t>INE134E08LK2</t>
-  </si>
-  <si>
-    <t>INE134E08LP1</t>
-  </si>
-  <si>
-    <t>INE134E08LD7</t>
-  </si>
-  <si>
-    <t>INE153A08089</t>
-  </si>
-  <si>
-    <t>BWR AA+(CE)</t>
-  </si>
-  <si>
-    <t>INE020B08ES7</t>
-  </si>
-  <si>
-    <t>INE040A08484</t>
-  </si>
-  <si>
-    <t>Indian Railway Finance Corporation Ltd. **</t>
+    <t>INE020B08AC9</t>
+  </si>
+  <si>
+    <t>INE134E08MC7</t>
+  </si>
+  <si>
+    <t>INE020B08FC8</t>
+  </si>
+  <si>
+    <t>INE134E08IE1</t>
+  </si>
+  <si>
+    <t>INE134E08II2</t>
+  </si>
+  <si>
+    <t>INE134E08ML8</t>
   </si>
   <si>
     <t>INE053F08288</t>
   </si>
   <si>
-    <t>INE134E08MT1</t>
-  </si>
-  <si>
-    <t>INE020B08EM0</t>
-  </si>
-  <si>
-    <t>Power Finance Corporation Ltd.</t>
-  </si>
-  <si>
-    <t>INE134E08LO4</t>
-  </si>
-  <si>
-    <t>Citicorp Finance (India) Ltd. **</t>
-  </si>
-  <si>
-    <t>INE915D08CY6</t>
-  </si>
-  <si>
-    <t>INE062A08264</t>
-  </si>
-  <si>
-    <t>INE556F08KU4</t>
-  </si>
-  <si>
-    <t>INE238A08450</t>
-  </si>
-  <si>
-    <t>INE134E08JP5</t>
-  </si>
-  <si>
-    <t>Bharat Sanchar Nigam Ltd. **</t>
-  </si>
-  <si>
-    <t>INE103D08054</t>
-  </si>
-  <si>
-    <t>CRISIL AAA(CE)</t>
-  </si>
-  <si>
-    <t>INE040A08542</t>
-  </si>
-  <si>
-    <t>INE556F08KN9</t>
-  </si>
-  <si>
-    <t>INE261F08EF5</t>
-  </si>
-  <si>
-    <t>LIC Housing Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE115A07RB7</t>
-  </si>
-  <si>
-    <t>INE040A08955</t>
-  </si>
-  <si>
-    <t>INE020B08EA5</t>
-  </si>
-  <si>
-    <t>INE031A08855</t>
-  </si>
-  <si>
-    <t>INE020B08ET5</t>
-  </si>
-  <si>
-    <t>Canara Bank ( Tier II Bond under Basel III ) **</t>
-  </si>
-  <si>
-    <t>INE476A08076</t>
-  </si>
-  <si>
-    <t>FITCH AAA</t>
-  </si>
-  <si>
-    <t>INE040A08708</t>
-  </si>
-  <si>
-    <t>Kotak Mahindra Bank Ltd. **</t>
-  </si>
-  <si>
-    <t>INE237A08940</t>
-  </si>
-  <si>
-    <t>INE040A08807</t>
-  </si>
-  <si>
-    <t>INE0J7Q07017</t>
-  </si>
-  <si>
-    <t>INE0J7Q07108</t>
-  </si>
-  <si>
-    <t>INE0J7Q07074</t>
-  </si>
-  <si>
-    <t>INE0J7Q07082</t>
-  </si>
-  <si>
-    <t>INE0J7Q07090</t>
-  </si>
-  <si>
-    <t>INE0J7Q07066</t>
-  </si>
-  <si>
-    <t>INE0J7Q07058</t>
-  </si>
-  <si>
-    <t>INE0J7Q07041</t>
-  </si>
-  <si>
-    <t>INE0J7Q07033</t>
-  </si>
-  <si>
-    <t>INE0J7Q07025</t>
-  </si>
-  <si>
-    <t>INE134E08LX5</t>
-  </si>
-  <si>
-    <t>INE134E08MJ2</t>
-  </si>
-  <si>
-    <t>INE134E08IE1</t>
-  </si>
-  <si>
-    <t>INE261F08EI9</t>
-  </si>
-  <si>
-    <t>INE134E08MC7</t>
-  </si>
-  <si>
-    <t>HDB Financial Services Ltd. **</t>
-  </si>
-  <si>
-    <t>INE756I07EL8</t>
-  </si>
-  <si>
-    <t>INE020B08FC8</t>
-  </si>
-  <si>
-    <t>INE134E08ML8</t>
+    <t>INE556F08KG3</t>
+  </si>
+  <si>
+    <t>INE134E08LG0</t>
   </si>
   <si>
     <t>ICICI Home Finance Company Ltd. **</t>
@@ -411,52 +477,25 @@
     <t>INE071G07777</t>
   </si>
   <si>
-    <t>INE556F08KG3</t>
-  </si>
-  <si>
-    <t>INE556F08KJ7</t>
-  </si>
-  <si>
-    <t>INE261F08EA6</t>
-  </si>
-  <si>
-    <t>Chennai Petroleum Corporation Ltd. **</t>
-  </si>
-  <si>
-    <t>INE178A08029</t>
-  </si>
-  <si>
-    <t>ICICI Bank Ltd. ( Tier II Bond under Basel III ) **</t>
-  </si>
-  <si>
-    <t>INE090A08UD0</t>
-  </si>
-  <si>
-    <t>INE756I07EN4</t>
-  </si>
-  <si>
-    <t>INE556F08KK5</t>
-  </si>
-  <si>
-    <t>INE134E08II2</t>
-  </si>
-  <si>
-    <t>INE556F08KT6</t>
+    <t>INE556F08KL3</t>
   </si>
   <si>
     <t>INE020B08AA3</t>
   </si>
   <si>
-    <t>INE020B08963</t>
-  </si>
-  <si>
-    <t>INE134E08LR7</t>
+    <t>ICICI Bank Ltd. **</t>
+  </si>
+  <si>
+    <t>INE090A08UE8</t>
+  </si>
+  <si>
+    <t>INE053F08338</t>
   </si>
   <si>
     <t>INE020B08443</t>
   </si>
   <si>
-    <t>INE261F08DT8</t>
+    <t>INE261F08EB4</t>
   </si>
   <si>
     <t>Zero Coupon Bonds / Deep Discount Bonds</t>
@@ -489,18 +528,18 @@
     <t>India Universal Trust AL2 **</t>
   </si>
   <si>
+    <t>INE1CBK15037</t>
+  </si>
+  <si>
+    <t>CRISIL AAA(SO)</t>
+  </si>
+  <si>
+    <t>INE1CBK15029</t>
+  </si>
+  <si>
     <t>INE1CBK15011</t>
   </si>
   <si>
-    <t>CRISIL AAA(SO)</t>
-  </si>
-  <si>
-    <t>INE1CBK15029</t>
-  </si>
-  <si>
-    <t>INE1CBK15037</t>
-  </si>
-  <si>
     <t>Term Deposits</t>
   </si>
   <si>
@@ -516,39 +555,27 @@
     <t>Certificate of Deposits</t>
   </si>
   <si>
+    <t>IDFC First Bank Ltd. **</t>
+  </si>
+  <si>
+    <t>INE092T16YI0</t>
+  </si>
+  <si>
+    <t>CRISIL A1+</t>
+  </si>
+  <si>
     <t>Punjab National Bank **</t>
   </si>
   <si>
     <t>INE160A16QT8</t>
   </si>
   <si>
-    <t>CRISIL A1+</t>
-  </si>
-  <si>
-    <t>INE238AD6AE9</t>
-  </si>
-  <si>
-    <t>INE556F16AV6</t>
-  </si>
-  <si>
-    <t>HDFC Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE040A16GA3</t>
-  </si>
-  <si>
-    <t>INE238AD6868</t>
+    <t>INE238AD6AM2</t>
   </si>
   <si>
     <t>Commercial Papers</t>
   </si>
   <si>
-    <t>Export-Import Bank Of India **</t>
-  </si>
-  <si>
-    <t>INE514E14SO0</t>
-  </si>
-  <si>
     <t>Bills Rediscounted</t>
   </si>
   <si>
@@ -576,12 +603,57 @@
     <t>Total Net Assets</t>
   </si>
   <si>
+    <t xml:space="preserve">INTEREST RATE SWAPS (At Notional Value) </t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -09-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> BNP Paribas- MD -09-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -14-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t>GSCCIL- MD -23-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -23-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> ICICI Securities Primary Dealership Ltd.- MD -29-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Hongkong and Shanghai Banking Corporation Ltd.- MD -29-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Standard Chartered Bank- MD -12-Mar-2027 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Standard Chartered Bank- MD -14-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Hongkong and Shanghai Banking Corporation Ltd.- MD -06-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -24-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> BNP Paribas- MD -24-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> BNP Paribas- MD -14-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
     <t>** Non Traded / Illiquid Securities.</t>
   </si>
   <si>
+    <t>^ Value Less than 0.01% of NAV in absolute terms.</t>
+  </si>
+  <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
   </si>
   <si>
@@ -591,7 +663,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -606,7 +678,7 @@
     <t>Benchmark Riskometer</t>
   </si>
   <si>
-    <t>Benchmark name - Nifty Banking &amp; PSU Debt Index A-II</t>
+    <t>Benchmark name - CRISIL Banking and PSU Debt Index</t>
   </si>
   <si>
     <t>Mahanagar Telephone Nigam Ltd. ** #</t>
@@ -619,14 +691,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="##0.00"/>
     <numFmt numFmtId="165" formatCode="##0.00%"/>
-    <numFmt numFmtId="166" formatCode="##0"/>
+    <numFmt numFmtId="166" formatCode="\^"/>
+    <numFmt numFmtId="167" formatCode="##0"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -710,7 +783,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -804,6 +877,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -813,8 +895,19 @@
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
@@ -826,17 +919,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
@@ -868,7 +950,7 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -877,12 +959,16 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
@@ -915,13 +1001,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>162</xdr:row>
+      <xdr:row>189</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>172</xdr:row>
+      <xdr:row>199</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -939,8 +1025,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="31737300"/>
-          <a:ext cx="3705225" cy="1905000"/>
+          <a:off x="666750" y="36699825"/>
+          <a:ext cx="6419850" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -956,13 +1042,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>177</xdr:row>
+      <xdr:row>204</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>187</xdr:row>
+      <xdr:row>214</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -980,8 +1066,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="34594800"/>
-          <a:ext cx="3705225" cy="1905000"/>
+          <a:off x="666750" y="39557325"/>
+          <a:ext cx="6419850" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1316,59 +1402,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J176"/>
+  <dimension ref="A1:J203"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" style="26" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="55.5546875" style="26" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.88671875" style="26" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="9.6640625" style="26" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="19.6640625" style="26" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="11.109375" style="26" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="38.6640625" style="26" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="11.6640625" style="26" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="29.6640625" style="26" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="26.6640625" style="26" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="10" style="28" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="96.33203125" style="28" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="17" style="28" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="9.6640625" style="28" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="19.6640625" style="28" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="11.109375" style="28" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="38.6640625" style="28" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="11.6640625" style="28" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="29.6640625" style="28" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="26.6640625" style="28" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
     </row>
     <row r="2" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
     </row>
     <row r="3" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
     </row>
     <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
@@ -1416,10 +1502,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="13">
-        <v>914961.95999999938</v>
+        <v>989714.17000000016</v>
       </c>
       <c r="H5" s="14">
-        <v>0.91680381160169988</v>
+        <v>0.94391293012820032</v>
       </c>
       <c r="I5" s="13" t="s">
         <v>13</v>
@@ -1453,10 +1539,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="13">
-        <v>887226.57999999949</v>
+        <v>964674.9800000001</v>
       </c>
       <c r="H7" s="14">
-        <v>0.88901259927629983</v>
+        <v>0.92003248472560029</v>
       </c>
       <c r="I7" s="13" t="s">
         <v>13</v>
@@ -1490,10 +1576,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="13">
-        <v>138200.54999999999</v>
+        <v>149635.28999999998</v>
       </c>
       <c r="H9" s="14">
-        <v>0.13847875271859997</v>
+        <v>0.14271058181860002</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>13</v>
@@ -1516,16 +1602,16 @@
         <v>17</v>
       </c>
       <c r="F10" s="19">
-        <v>73909360</v>
+        <v>47268860</v>
       </c>
       <c r="G10" s="20">
-        <v>75687.91</v>
+        <v>49829.89</v>
       </c>
       <c r="H10" s="21">
-        <v>7.5840272507600004E-2</v>
+        <v>4.75239002369E-2</v>
       </c>
       <c r="I10" s="20">
-        <v>6.86</v>
+        <v>6.39</v>
       </c>
       <c r="J10" s="15" t="s">
         <v>13</v>
@@ -1539,22 +1625,22 @@
         <v>18</v>
       </c>
       <c r="D11" s="18">
-        <v>7.9300000000000006</v>
+        <v>7.34</v>
       </c>
       <c r="E11" s="17" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="19">
-        <v>48934850</v>
+        <v>33467800</v>
       </c>
       <c r="G11" s="20">
-        <v>50188.37</v>
+        <v>35624.26</v>
       </c>
       <c r="H11" s="21">
-        <v>5.02894010088E-2</v>
+        <v>3.3975667581300002E-2</v>
       </c>
       <c r="I11" s="20">
-        <v>7.66</v>
+        <v>6.98</v>
       </c>
       <c r="J11" s="15" t="s">
         <v>13</v>
@@ -1568,22 +1654,22 @@
         <v>19</v>
       </c>
       <c r="D12" s="18">
-        <v>7.53</v>
+        <v>7.81</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="19">
-        <v>11666820</v>
+        <v>28276430</v>
       </c>
       <c r="G12" s="20">
-        <v>11751.84</v>
+        <v>29363.43</v>
       </c>
       <c r="H12" s="21">
-        <v>1.17754968801E-2</v>
+        <v>2.8004571511800001E-2</v>
       </c>
       <c r="I12" s="20">
-        <v>7.47</v>
+        <v>7.31</v>
       </c>
       <c r="J12" s="15" t="s">
         <v>13</v>
@@ -1597,22 +1683,22 @@
         <v>20</v>
       </c>
       <c r="D13" s="18">
-        <v>6.92</v>
+        <v>6.99</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="19">
-        <v>281800</v>
+        <v>8666820</v>
       </c>
       <c r="G13" s="20">
-        <v>284.27999999999997</v>
+        <v>8846.7800000000007</v>
       </c>
       <c r="H13" s="21">
-        <v>2.8485226589999998E-4</v>
+        <v>8.4373754414000003E-3</v>
       </c>
       <c r="I13" s="20">
-        <v>6.94</v>
+        <v>6.8</v>
       </c>
       <c r="J13" s="15" t="s">
         <v>13</v>
@@ -1626,22 +1712,22 @@
         <v>21</v>
       </c>
       <c r="D14" s="18">
-        <v>7.18</v>
+        <v>6.79</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="19">
-        <v>151060</v>
+        <v>5516660</v>
       </c>
       <c r="G14" s="20">
-        <v>155.19</v>
+        <v>5714.87</v>
       </c>
       <c r="H14" s="21">
-        <v>1.5550240300000001E-4</v>
+        <v>5.4504015912000001E-3</v>
       </c>
       <c r="I14" s="20">
-        <v>6.87</v>
+        <v>6.37</v>
       </c>
       <c r="J14" s="15" t="s">
         <v>13</v>
@@ -1649,28 +1735,28 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="16" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" s="18">
-        <v>6.79</v>
+        <v>7.12</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>17</v>
       </c>
       <c r="F15" s="19">
-        <v>77400</v>
+        <v>4960700</v>
       </c>
       <c r="G15" s="20">
-        <v>77.91</v>
+        <v>5127.57</v>
       </c>
       <c r="H15" s="21">
-        <v>7.8066835599999995E-5</v>
+        <v>4.8902802141000002E-3</v>
       </c>
       <c r="I15" s="20">
-        <v>6.81</v>
+        <v>6.83</v>
       </c>
       <c r="J15" s="15" t="s">
         <v>13</v>
@@ -1678,28 +1764,28 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>24</v>
       </c>
       <c r="D16" s="18">
-        <v>8.0500000000000007</v>
+        <v>6.9</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>17</v>
       </c>
       <c r="F16" s="19">
-        <v>55000</v>
+        <v>5000000</v>
       </c>
       <c r="G16" s="20">
-        <v>55.05</v>
+        <v>5033.66</v>
       </c>
       <c r="H16" s="21">
-        <v>5.5160817599999998E-5</v>
+        <v>4.8007161096000001E-3</v>
       </c>
       <c r="I16" s="20">
-        <v>6.67</v>
+        <v>6.97</v>
       </c>
       <c r="J16" s="15" t="s">
         <v>13</v>
@@ -1707,36 +1793,57 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="16" t="s">
-        <v>13</v>
+        <v>22</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="18">
+        <v>7.1400000000000006</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="19">
+        <v>4000000</v>
+      </c>
+      <c r="G17" s="20">
+        <v>4151.0200000000004</v>
+      </c>
+      <c r="H17" s="21">
+        <v>3.9589222525000002E-3</v>
+      </c>
+      <c r="I17" s="20">
+        <v>6.82</v>
       </c>
       <c r="J17" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="13">
-        <v>749026.02999999968</v>
-      </c>
-      <c r="H18" s="14">
-        <v>0.75053384655769995</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>13</v>
+      <c r="B18" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="18">
+        <v>7.32</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="19">
+        <v>2762800</v>
+      </c>
+      <c r="G18" s="20">
+        <v>2899.91</v>
+      </c>
+      <c r="H18" s="21">
+        <v>2.7657101697999998E-3</v>
+      </c>
+      <c r="I18" s="20">
+        <v>6.81</v>
       </c>
       <c r="J18" s="15" t="s">
         <v>13</v>
@@ -1744,28 +1851,28 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D19" s="18">
-        <v>7.25</v>
+        <v>7.13</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F19" s="19">
-        <v>4750</v>
+        <v>2329600</v>
       </c>
       <c r="G19" s="20">
-        <v>47321.919999999998</v>
+        <v>2406.36</v>
       </c>
       <c r="H19" s="21">
-        <v>4.7417180741000001E-2</v>
+        <v>2.2950003015E-3</v>
       </c>
       <c r="I19" s="20">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>13</v>
@@ -1773,28 +1880,28 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D20" s="18">
-        <v>7.58</v>
+        <v>7.29</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F20" s="19">
-        <v>40500</v>
+        <v>577700</v>
       </c>
       <c r="G20" s="20">
-        <v>40444.19</v>
+        <v>603.04</v>
       </c>
       <c r="H20" s="21">
-        <v>4.0525605621099997E-2</v>
+        <v>5.7513297329999996E-4</v>
       </c>
       <c r="I20" s="20">
-        <v>7.63</v>
+        <v>6.88</v>
       </c>
       <c r="J20" s="15" t="s">
         <v>13</v>
@@ -1802,28 +1909,28 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="D21" s="18">
+        <v>6.92</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="19">
+        <v>32950</v>
+      </c>
+      <c r="G21" s="20">
+        <v>34.5</v>
+      </c>
+      <c r="H21" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="18">
-        <v>7.75</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" s="19">
-        <v>37800</v>
-      </c>
-      <c r="G21" s="20">
-        <v>38544.58</v>
-      </c>
-      <c r="H21" s="21">
-        <v>3.8622171637300001E-2</v>
-      </c>
       <c r="I21" s="20">
-        <v>7.42</v>
+        <v>6.52</v>
       </c>
       <c r="J21" s="15" t="s">
         <v>13</v>
@@ -1831,57 +1938,36 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="18">
-        <v>6.24</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="F22" s="19">
-        <v>3400</v>
-      </c>
-      <c r="G22" s="20">
-        <v>33657.18</v>
-      </c>
-      <c r="H22" s="21">
-        <v>3.37249331239E-2</v>
-      </c>
-      <c r="I22" s="20">
-        <v>6.45</v>
-      </c>
-      <c r="J22" s="15">
-        <v>7.74</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="18">
-        <v>7.57</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="F23" s="19">
-        <v>26000</v>
-      </c>
-      <c r="G23" s="20">
-        <v>25960.79</v>
-      </c>
-      <c r="H23" s="21">
-        <v>2.6013050011700001E-2</v>
-      </c>
-      <c r="I23" s="20">
-        <v>7.69</v>
+      <c r="C23" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="13">
+        <v>815039.69</v>
+      </c>
+      <c r="H23" s="14">
+        <v>0.7773219029070001</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="J23" s="15" t="s">
         <v>13</v>
@@ -1889,28 +1975,28 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="16" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D24" s="18">
-        <v>7.61</v>
+        <v>7.58</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F24" s="19">
-        <v>25000</v>
+        <v>45500</v>
       </c>
       <c r="G24" s="20">
-        <v>25166.38</v>
+        <v>45959.23</v>
       </c>
       <c r="H24" s="21">
-        <v>2.5217040835599999E-2</v>
+        <v>4.3832363697399998E-2</v>
       </c>
       <c r="I24" s="20">
-        <v>7.5</v>
+        <v>6.62</v>
       </c>
       <c r="J24" s="15" t="s">
         <v>13</v>
@@ -1918,28 +2004,28 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="16" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D25" s="18">
-        <v>7.8</v>
+        <v>7.75</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F25" s="19">
-        <v>22500</v>
+        <v>40800</v>
       </c>
       <c r="G25" s="20">
-        <v>22201.759999999998</v>
+        <v>42566.68</v>
       </c>
       <c r="H25" s="21">
-        <v>2.2246452948000001E-2</v>
+        <v>4.0596811546900001E-2</v>
       </c>
       <c r="I25" s="20">
-        <v>8.17</v>
+        <v>7.03</v>
       </c>
       <c r="J25" s="15" t="s">
         <v>13</v>
@@ -1947,57 +2033,57 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="16" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D26" s="18">
-        <v>7.58</v>
+        <v>6.24</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F26" s="19">
-        <v>20000</v>
+        <v>3400</v>
       </c>
       <c r="G26" s="20">
-        <v>20028.5</v>
+        <v>34023.9</v>
       </c>
       <c r="H26" s="21">
-        <v>2.0068818096800001E-2</v>
+        <v>3.2449367824599999E-2</v>
       </c>
       <c r="I26" s="20">
-        <v>7.42</v>
-      </c>
-      <c r="J26" s="15" t="s">
-        <v>13</v>
+        <v>6.22</v>
+      </c>
+      <c r="J26" s="15">
+        <v>5.76</v>
       </c>
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="16" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D27" s="18">
-        <v>7.51</v>
+        <v>7.61</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F27" s="19">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="G27" s="20">
-        <v>19960.36</v>
+        <v>25763.599999999999</v>
       </c>
       <c r="H27" s="21">
-        <v>2.00005409285E-2</v>
+        <v>2.4571331707600001E-2</v>
       </c>
       <c r="I27" s="20">
-        <v>7.61</v>
+        <v>7.14</v>
       </c>
       <c r="J27" s="15" t="s">
         <v>13</v>
@@ -2005,28 +2091,28 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="16" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D28" s="18">
-        <v>7.37</v>
+        <v>7.58</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F28" s="19">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="G28" s="20">
-        <v>19923.939999999999</v>
+        <v>25625.03</v>
       </c>
       <c r="H28" s="21">
-        <v>1.9964047613699999E-2</v>
+        <v>2.4439174344699999E-2</v>
       </c>
       <c r="I28" s="20">
-        <v>7.64</v>
+        <v>7.21</v>
       </c>
       <c r="J28" s="15" t="s">
         <v>13</v>
@@ -2034,28 +2120,28 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="16" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D29" s="18">
-        <v>7.86</v>
+        <v>7.53</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F29" s="19">
-        <v>187</v>
+        <v>22500</v>
       </c>
       <c r="G29" s="20">
-        <v>19048.099999999999</v>
+        <v>23007.42</v>
       </c>
       <c r="H29" s="21">
-        <v>1.9086444516000001E-2</v>
+        <v>2.1942700110000001E-2</v>
       </c>
       <c r="I29" s="20">
-        <v>7.53</v>
+        <v>6.61</v>
       </c>
       <c r="J29" s="15" t="s">
         <v>13</v>
@@ -2063,57 +2149,57 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="16" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D30" s="18">
-        <v>6.18</v>
+        <v>7.8</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="F30" s="19">
-        <v>1850</v>
+        <v>22500</v>
       </c>
       <c r="G30" s="20">
-        <v>18176.23</v>
+        <v>22820.81</v>
       </c>
       <c r="H30" s="21">
-        <v>1.8212819410100001E-2</v>
+        <v>2.17647259057E-2</v>
       </c>
       <c r="I30" s="20">
-        <v>6.54</v>
-      </c>
-      <c r="J30" s="15">
-        <v>8.14</v>
+        <v>7.71</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D31" s="18">
         <v>7.68</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F31" s="19">
-        <v>17500</v>
+        <v>20000</v>
       </c>
       <c r="G31" s="20">
-        <v>17549.79</v>
+        <v>20455.86</v>
       </c>
       <c r="H31" s="21">
-        <v>1.7585118363700001E-2</v>
+        <v>1.9509219263700001E-2</v>
       </c>
       <c r="I31" s="20">
-        <v>7.39</v>
+        <v>6.58</v>
       </c>
       <c r="J31" s="15" t="s">
         <v>13</v>
@@ -2121,28 +2207,28 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="16" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D32" s="18">
-        <v>7.53</v>
+        <v>7.51</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F32" s="19">
-        <v>17500</v>
+        <v>20000</v>
       </c>
       <c r="G32" s="20">
-        <v>17520.810000000001</v>
+        <v>20202.14</v>
       </c>
       <c r="H32" s="21">
-        <v>1.7556080025899999E-2</v>
+        <v>1.9267240724999999E-2</v>
       </c>
       <c r="I32" s="20">
-        <v>7.5</v>
+        <v>6.55</v>
       </c>
       <c r="J32" s="15" t="s">
         <v>13</v>
@@ -2150,28 +2236,28 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="16" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C33" s="17" t="s">
         <v>56</v>
       </c>
       <c r="D33" s="18">
-        <v>7.56</v>
+        <v>7.58</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F33" s="19">
-        <v>16500</v>
+        <v>20000</v>
       </c>
       <c r="G33" s="20">
-        <v>16475.09</v>
+        <v>20161.86</v>
       </c>
       <c r="H33" s="21">
-        <v>1.6508254953600001E-2</v>
+        <v>1.92288247722E-2</v>
       </c>
       <c r="I33" s="20">
-        <v>7.63</v>
+        <v>6.41</v>
       </c>
       <c r="J33" s="15" t="s">
         <v>13</v>
@@ -2179,28 +2265,28 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="16" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D34" s="18">
         <v>7.44</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F34" s="19">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="G34" s="20">
-        <v>14963.61</v>
+        <v>20156.46</v>
       </c>
       <c r="H34" s="21">
-        <v>1.49937322895E-2</v>
+        <v>1.92236746693E-2</v>
       </c>
       <c r="I34" s="20">
-        <v>7.63</v>
+        <v>6.55</v>
       </c>
       <c r="J34" s="15" t="s">
         <v>13</v>
@@ -2208,28 +2294,28 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="16" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D35" s="18">
-        <v>7.8</v>
+        <v>7.37</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F35" s="19">
-        <v>13000</v>
+        <v>20000</v>
       </c>
       <c r="G35" s="20">
-        <v>13294.06</v>
+        <v>20147.54</v>
       </c>
       <c r="H35" s="21">
-        <v>1.3320821424800001E-2</v>
+        <v>1.9215167462299999E-2</v>
       </c>
       <c r="I35" s="20">
-        <v>7.42</v>
+        <v>6.55</v>
       </c>
       <c r="J35" s="15" t="s">
         <v>13</v>
@@ -2237,28 +2323,28 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="16" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D36" s="18">
-        <v>7.44</v>
+        <v>7.86</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F36" s="19">
-        <v>12500</v>
+        <v>192</v>
       </c>
       <c r="G36" s="20">
-        <v>12477.9</v>
+        <v>20060.849999999999</v>
       </c>
       <c r="H36" s="21">
-        <v>1.2503018465199999E-2</v>
+        <v>1.91324892362E-2</v>
       </c>
       <c r="I36" s="20">
-        <v>7.7</v>
+        <v>7.06</v>
       </c>
       <c r="J36" s="15" t="s">
         <v>13</v>
@@ -2266,57 +2352,57 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="16" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D37" s="18">
-        <v>7.44</v>
+        <v>6.18</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F37" s="19">
-        <v>12500</v>
+        <v>1850</v>
       </c>
       <c r="G37" s="20">
-        <v>12461.05</v>
+        <v>18460.04</v>
       </c>
       <c r="H37" s="21">
-        <v>1.2486134545500001E-2</v>
+        <v>1.76057603042E-2</v>
       </c>
       <c r="I37" s="20">
-        <v>7.61</v>
-      </c>
-      <c r="J37" s="15" t="s">
-        <v>13</v>
+        <v>6.22</v>
+      </c>
+      <c r="J37" s="15">
+        <v>6.39</v>
       </c>
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="16" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D38" s="18">
-        <v>7.6</v>
+        <v>7.68</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F38" s="19">
-        <v>12000</v>
+        <v>17500</v>
       </c>
       <c r="G38" s="20">
-        <v>11991.22</v>
+        <v>17685.900000000001</v>
       </c>
       <c r="H38" s="21">
-        <v>1.20153587607E-2</v>
+        <v>1.6867445366599999E-2</v>
       </c>
       <c r="I38" s="20">
-        <v>7.66</v>
+        <v>6.48</v>
       </c>
       <c r="J38" s="15" t="s">
         <v>13</v>
@@ -2324,28 +2410,28 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="16" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D39" s="18">
-        <v>7.62</v>
+        <v>7.56</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F39" s="19">
-        <v>11500</v>
+        <v>17000</v>
       </c>
       <c r="G39" s="20">
-        <v>11532.45</v>
+        <v>17169.64</v>
       </c>
       <c r="H39" s="21">
-        <v>1.155566524E-2</v>
+        <v>1.6375076454299999E-2</v>
       </c>
       <c r="I39" s="20">
-        <v>7.5</v>
+        <v>6.56</v>
       </c>
       <c r="J39" s="15" t="s">
         <v>13</v>
@@ -2353,28 +2439,28 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="16" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D40" s="18">
-        <v>7.65</v>
+        <v>7.51</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F40" s="19">
-        <v>1100</v>
+        <v>15500</v>
       </c>
       <c r="G40" s="20">
-        <v>10999.84</v>
+        <v>15877.19</v>
       </c>
       <c r="H40" s="21">
-        <v>1.1021983076799999E-2</v>
+        <v>1.51424374728E-2</v>
       </c>
       <c r="I40" s="20">
-        <v>7.65</v>
+        <v>6.59</v>
       </c>
       <c r="J40" s="15" t="s">
         <v>13</v>
@@ -2382,28 +2468,28 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="16" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D41" s="18">
-        <v>7.55</v>
+        <v>7.7</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F41" s="19">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="G41" s="20">
-        <v>10204.469999999999</v>
+        <v>15341.52</v>
       </c>
       <c r="H41" s="21">
-        <v>1.02250119681E-2</v>
+        <v>1.46315568018E-2</v>
       </c>
       <c r="I41" s="20">
-        <v>7.45</v>
+        <v>6.59</v>
       </c>
       <c r="J41" s="15" t="s">
         <v>13</v>
@@ -2411,28 +2497,28 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="16" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D42" s="18">
-        <v>7.7120000000000006</v>
+        <v>7.44</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F42" s="19">
-        <v>10000</v>
+        <v>14900</v>
       </c>
       <c r="G42" s="20">
-        <v>9995.07</v>
+        <v>15038.29</v>
       </c>
       <c r="H42" s="21">
-        <v>1.0015190438300001E-2</v>
+        <v>1.4342359449099999E-2</v>
       </c>
       <c r="I42" s="20">
-        <v>7.73</v>
+        <v>6.61</v>
       </c>
       <c r="J42" s="15" t="s">
         <v>13</v>
@@ -2440,28 +2526,28 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="16" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D43" s="18">
-        <v>7.43</v>
+        <v>7.8</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F43" s="19">
-        <v>10000</v>
+        <v>14000</v>
       </c>
       <c r="G43" s="20">
-        <v>9963.19</v>
+        <v>14639.74</v>
       </c>
       <c r="H43" s="21">
-        <v>9.9832462627000001E-3</v>
+        <v>1.3962253242999999E-2</v>
       </c>
       <c r="I43" s="20">
-        <v>7.64</v>
+        <v>7.03</v>
       </c>
       <c r="J43" s="15" t="s">
         <v>13</v>
@@ -2469,28 +2555,28 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D44" s="18">
-        <v>6.09</v>
+        <v>7.62</v>
       </c>
       <c r="E44" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F44" s="19">
-        <v>1000</v>
+        <v>14000</v>
       </c>
       <c r="G44" s="20">
-        <v>9776.25</v>
+        <v>14326.68</v>
       </c>
       <c r="H44" s="21">
-        <v>9.7959299456999993E-3</v>
+        <v>1.36636807957E-2</v>
       </c>
       <c r="I44" s="20">
-        <v>7.62</v>
+        <v>6.61</v>
       </c>
       <c r="J44" s="15" t="s">
         <v>13</v>
@@ -2498,28 +2584,28 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="16" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D45" s="18">
         <v>7.13</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F45" s="19">
-        <v>950</v>
+        <v>1300</v>
       </c>
       <c r="G45" s="20">
-        <v>9434.4</v>
+        <v>13076.45</v>
       </c>
       <c r="H45" s="21">
-        <v>9.4533917893000006E-3</v>
+        <v>1.2471307989100001E-2</v>
       </c>
       <c r="I45" s="20">
-        <v>7.62</v>
+        <v>6.55</v>
       </c>
       <c r="J45" s="15" t="s">
         <v>13</v>
@@ -2527,28 +2613,28 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="16" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D46" s="18">
-        <v>6.5</v>
+        <v>7.69</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F46" s="19">
-        <v>850</v>
+        <v>12500</v>
       </c>
       <c r="G46" s="20">
-        <v>8425.57</v>
+        <v>12898.64</v>
       </c>
       <c r="H46" s="21">
-        <v>8.4425309779000007E-3</v>
+        <v>1.2301726545000001E-2</v>
       </c>
       <c r="I46" s="20">
-        <v>7.78</v>
+        <v>7.13</v>
       </c>
       <c r="J46" s="15" t="s">
         <v>13</v>
@@ -2556,28 +2642,28 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="16" t="s">
-        <v>196</v>
+        <v>51</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D47" s="18">
-        <v>7.05</v>
+        <v>7.75</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="F47" s="19">
-        <v>831</v>
+        <v>12500</v>
       </c>
       <c r="G47" s="20">
-        <v>7969.65</v>
+        <v>12770.89</v>
       </c>
       <c r="H47" s="21">
-        <v>7.9856931943999999E-3</v>
+        <v>1.21798884624E-2</v>
       </c>
       <c r="I47" s="20">
-        <v>8.11</v>
+        <v>6.57</v>
       </c>
       <c r="J47" s="15" t="s">
         <v>13</v>
@@ -2585,28 +2671,28 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="16" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D48" s="18">
-        <v>7.8</v>
+        <v>7.43</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F48" s="19">
-        <v>7500</v>
+        <v>12500</v>
       </c>
       <c r="G48" s="20">
-        <v>7511.27</v>
+        <v>12613.7</v>
       </c>
       <c r="H48" s="21">
-        <v>7.5263904588999996E-3</v>
+        <v>1.20299727817E-2</v>
       </c>
       <c r="I48" s="20">
-        <v>7.63</v>
+        <v>6.61</v>
       </c>
       <c r="J48" s="15" t="s">
         <v>13</v>
@@ -2614,57 +2700,57 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="16" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D49" s="18">
-        <v>7.9</v>
+        <v>5.83</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F49" s="19">
-        <v>75</v>
+        <v>1100</v>
       </c>
       <c r="G49" s="20">
-        <v>7507.29</v>
+        <v>10945.06</v>
       </c>
       <c r="H49" s="21">
-        <v>7.5224024469999996E-3</v>
+        <v>1.04385528349E-2</v>
       </c>
       <c r="I49" s="20">
-        <v>7.78</v>
-      </c>
-      <c r="J49" s="15" t="s">
-        <v>13</v>
+        <v>5.93</v>
+      </c>
+      <c r="J49" s="15">
+        <v>6.88</v>
       </c>
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D50" s="18">
-        <v>7.51</v>
+        <v>7.55</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F50" s="19">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="G50" s="20">
-        <v>7497</v>
+        <v>10461.4</v>
       </c>
       <c r="H50" s="21">
-        <v>7.5120917327999998E-3</v>
+        <v>9.9772752847000004E-3</v>
       </c>
       <c r="I50" s="20">
-        <v>7.55</v>
+        <v>7.14</v>
       </c>
       <c r="J50" s="15" t="s">
         <v>13</v>
@@ -2672,28 +2758,28 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D51" s="18">
-        <v>7.6400000000000006</v>
+        <v>7.44</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F51" s="19">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="G51" s="20">
-        <v>7496.96</v>
+        <v>10196.98</v>
       </c>
       <c r="H51" s="21">
-        <v>7.5120516523000001E-3</v>
+        <v>9.7250919123999992E-3</v>
       </c>
       <c r="I51" s="20">
-        <v>7.62</v>
+        <v>6.61</v>
       </c>
       <c r="J51" s="15" t="s">
         <v>13</v>
@@ -2701,28 +2787,28 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="16" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D52" s="18">
-        <v>7.6400000000000006</v>
+        <v>6.09</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F52" s="19">
-        <v>7500</v>
+        <v>1000</v>
       </c>
       <c r="G52" s="20">
-        <v>7496.36</v>
+        <v>9943.41</v>
       </c>
       <c r="H52" s="21">
-        <v>7.5114504445000004E-3</v>
+        <v>9.4832564321000005E-3</v>
       </c>
       <c r="I52" s="20">
-        <v>7.63</v>
+        <v>6.55</v>
       </c>
       <c r="J52" s="15" t="s">
         <v>13</v>
@@ -2730,28 +2816,28 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="16" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="C53" s="17" t="s">
         <v>83</v>
       </c>
       <c r="D53" s="18">
-        <v>7.13</v>
+        <v>7.44</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F53" s="19">
-        <v>700</v>
+        <v>9000</v>
       </c>
       <c r="G53" s="20">
-        <v>6968.25</v>
+        <v>9191.94</v>
       </c>
       <c r="H53" s="21">
-        <v>6.9822773398999999E-3</v>
+        <v>8.7665623894000004E-3</v>
       </c>
       <c r="I53" s="20">
-        <v>7.78</v>
+        <v>6.59</v>
       </c>
       <c r="J53" s="15" t="s">
         <v>13</v>
@@ -2759,28 +2845,28 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C54" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C54" s="17" t="s">
-        <v>85</v>
-      </c>
       <c r="D54" s="18">
-        <v>8.3000000000000007</v>
+        <v>7.79</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F54" s="19">
-        <v>6500</v>
+        <v>9000</v>
       </c>
       <c r="G54" s="20">
-        <v>6483.35</v>
+        <v>9188.43</v>
       </c>
       <c r="H54" s="21">
-        <v>6.4964012185999998E-3</v>
+        <v>8.7632148225000005E-3</v>
       </c>
       <c r="I54" s="20">
-        <v>9.09</v>
+        <v>6.57</v>
       </c>
       <c r="J54" s="15" t="s">
         <v>13</v>
@@ -2788,57 +2874,57 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="16" t="s">
-        <v>34</v>
+        <v>220</v>
       </c>
       <c r="C55" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D55" s="18">
+        <v>7.05</v>
+      </c>
+      <c r="E55" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="D55" s="18">
-        <v>5.83</v>
-      </c>
-      <c r="E55" s="17" t="s">
-        <v>31</v>
-      </c>
       <c r="F55" s="19">
-        <v>600</v>
+        <v>831</v>
       </c>
       <c r="G55" s="20">
-        <v>5890.19</v>
+        <v>8192.9</v>
       </c>
       <c r="H55" s="21">
-        <v>5.9020471659999999E-3</v>
+        <v>7.8137552028999992E-3</v>
       </c>
       <c r="I55" s="20">
-        <v>6.21</v>
-      </c>
-      <c r="J55" s="15">
-        <v>8.3699999999999992</v>
+        <v>7.51</v>
+      </c>
+      <c r="J55" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56" s="17" t="s">
         <v>87</v>
       </c>
       <c r="D56" s="18">
-        <v>7.51</v>
+        <v>7.6400000000000006</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F56" s="19">
-        <v>5500</v>
+        <v>7500</v>
       </c>
       <c r="G56" s="20">
-        <v>5506.97</v>
+        <v>7590.64</v>
       </c>
       <c r="H56" s="21">
-        <v>5.5180557303000002E-3</v>
+        <v>7.2393661333000001E-3</v>
       </c>
       <c r="I56" s="20">
-        <v>7.47</v>
+        <v>6.55</v>
       </c>
       <c r="J56" s="15" t="s">
         <v>13</v>
@@ -2846,28 +2932,28 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="16" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C57" s="17" t="s">
         <v>88</v>
       </c>
       <c r="D57" s="18">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F57" s="19">
-        <v>500</v>
+        <v>7500</v>
       </c>
       <c r="G57" s="20">
-        <v>5158.9399999999996</v>
+        <v>7587.08</v>
       </c>
       <c r="H57" s="21">
-        <v>5.1693251333000002E-3</v>
+        <v>7.2359708803E-3</v>
       </c>
       <c r="I57" s="20">
-        <v>7.62</v>
+        <v>6.56</v>
       </c>
       <c r="J57" s="15" t="s">
         <v>13</v>
@@ -2875,28 +2961,28 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="16" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C58" s="17" t="s">
         <v>89</v>
       </c>
       <c r="D58" s="18">
-        <v>7.85</v>
+        <v>7.6400000000000006</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F58" s="19">
-        <v>500</v>
+        <v>7500</v>
       </c>
       <c r="G58" s="20">
-        <v>5066.96</v>
+        <v>7580.89</v>
       </c>
       <c r="H58" s="21">
-        <v>5.0771599741999997E-3</v>
+        <v>7.2300673363999996E-3</v>
       </c>
       <c r="I58" s="20">
-        <v>7.5</v>
+        <v>6.56</v>
       </c>
       <c r="J58" s="15" t="s">
         <v>13</v>
@@ -2904,28 +2990,28 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C59" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="C59" s="17" t="s">
-        <v>91</v>
-      </c>
       <c r="D59" s="18">
-        <v>7.51</v>
+        <v>7.6</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="F59" s="19">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="G59" s="20">
-        <v>5055.95</v>
+        <v>7046.52</v>
       </c>
       <c r="H59" s="21">
-        <v>5.0661278107000003E-3</v>
+        <v>6.720426505E-3</v>
       </c>
       <c r="I59" s="20">
-        <v>7.47</v>
+        <v>6.54</v>
       </c>
       <c r="J59" s="15" t="s">
         <v>13</v>
@@ -2933,28 +3019,28 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="16" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="C60" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D60" s="18">
-        <v>8.4499999999999993</v>
+        <v>8.3500000000000014</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F60" s="19">
-        <v>50</v>
+        <v>6500</v>
       </c>
       <c r="G60" s="20">
-        <v>5034</v>
+        <v>6497.36</v>
       </c>
       <c r="H60" s="21">
-        <v>5.0441336244999996E-3</v>
+        <v>6.1966801139000001E-3</v>
       </c>
       <c r="I60" s="20">
-        <v>7.82</v>
+        <v>7.9</v>
       </c>
       <c r="J60" s="15" t="s">
         <v>13</v>
@@ -2962,28 +3048,28 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="16" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="C61" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D61" s="18">
-        <v>7.75</v>
+        <v>7.77</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F61" s="19">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="G61" s="20">
-        <v>5026.32</v>
+        <v>5667.72</v>
       </c>
       <c r="H61" s="21">
-        <v>5.0364381644000004E-3</v>
+        <v>5.4054335630000002E-3</v>
       </c>
       <c r="I61" s="20">
-        <v>7.52</v>
+        <v>6.56</v>
       </c>
       <c r="J61" s="15" t="s">
         <v>13</v>
@@ -2991,28 +3077,28 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="16" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="C62" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D62" s="18">
-        <v>7.8</v>
+        <v>7.85</v>
       </c>
       <c r="E62" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F62" s="19">
-        <v>5000</v>
+        <v>524</v>
       </c>
       <c r="G62" s="20">
-        <v>5022.71</v>
+        <v>5425.61</v>
       </c>
       <c r="H62" s="21">
-        <v>5.0328208973000003E-3</v>
+        <v>5.1745277455000002E-3</v>
       </c>
       <c r="I62" s="20">
-        <v>7.54</v>
+        <v>6.56</v>
       </c>
       <c r="J62" s="15" t="s">
         <v>13</v>
@@ -3020,28 +3106,28 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C63" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="C63" s="17" t="s">
-        <v>97</v>
-      </c>
       <c r="D63" s="18">
-        <v>7.58</v>
+        <v>8.6</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F63" s="19">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="G63" s="20">
-        <v>5020.17</v>
+        <v>5282.19</v>
       </c>
       <c r="H63" s="21">
-        <v>5.0302757841999999E-3</v>
+        <v>5.0377448272999996E-3</v>
       </c>
       <c r="I63" s="20">
-        <v>7.52</v>
+        <v>6.75</v>
       </c>
       <c r="J63" s="15" t="s">
         <v>13</v>
@@ -3049,28 +3135,28 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="16" t="s">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="C64" s="17" t="s">
         <v>98</v>
       </c>
       <c r="D64" s="18">
-        <v>7.7</v>
+        <v>7.51</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="F64" s="19">
         <v>5000</v>
       </c>
       <c r="G64" s="20">
-        <v>5007.87</v>
+        <v>5173.4399999999996</v>
       </c>
       <c r="H64" s="21">
-        <v>5.0179510238999997E-3</v>
+        <v>4.9340274770999998E-3</v>
       </c>
       <c r="I64" s="20">
-        <v>7.62</v>
+        <v>7.1</v>
       </c>
       <c r="J64" s="15" t="s">
         <v>13</v>
@@ -3078,28 +3164,28 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="16" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C65" s="17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D65" s="18">
-        <v>7.55</v>
+        <v>7.58</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F65" s="19">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="G65" s="20">
-        <v>5005.9399999999996</v>
+        <v>5146.63</v>
       </c>
       <c r="H65" s="21">
-        <v>5.0160171386999996E-3</v>
+        <v>4.9084581699000004E-3</v>
       </c>
       <c r="I65" s="20">
-        <v>7.49</v>
+        <v>7.14</v>
       </c>
       <c r="J65" s="15" t="s">
         <v>13</v>
@@ -3107,28 +3193,28 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="16" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C66" s="17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D66" s="18">
-        <v>7.54</v>
+        <v>7.55</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F66" s="19">
         <v>500</v>
       </c>
       <c r="G66" s="20">
-        <v>5005.0200000000004</v>
+        <v>5124.03</v>
       </c>
       <c r="H66" s="21">
-        <v>5.0150952867000003E-3</v>
+        <v>4.8869040354999997E-3</v>
       </c>
       <c r="I66" s="20">
-        <v>7.43</v>
+        <v>6.55</v>
       </c>
       <c r="J66" s="15" t="s">
         <v>13</v>
@@ -3136,28 +3222,28 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="16" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="C67" s="17" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D67" s="18">
-        <v>7.79</v>
+        <v>7.34</v>
       </c>
       <c r="E67" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F67" s="19">
         <v>5000</v>
       </c>
       <c r="G67" s="20">
-        <v>4998.68</v>
+        <v>5110.6899999999996</v>
       </c>
       <c r="H67" s="21">
-        <v>5.0087425241000004E-3</v>
+        <v>4.8741813739000004E-3</v>
       </c>
       <c r="I67" s="20">
-        <v>7.72</v>
+        <v>6.65</v>
       </c>
       <c r="J67" s="15" t="s">
         <v>13</v>
@@ -3165,57 +3251,57 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="16" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="C68" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D68" s="18">
-        <v>7.18</v>
+        <v>7.42</v>
       </c>
       <c r="E68" s="17" t="s">
-        <v>104</v>
+        <v>37</v>
       </c>
       <c r="F68" s="19">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="G68" s="20">
-        <v>4991.62</v>
+        <v>5108.29</v>
       </c>
       <c r="H68" s="21">
-        <v>5.0016683120000004E-3</v>
+        <v>4.8718924392000002E-3</v>
       </c>
       <c r="I68" s="20">
-        <v>7.21</v>
-      </c>
-      <c r="J68" s="15">
-        <v>8.27</v>
+        <v>6.56</v>
+      </c>
+      <c r="J68" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="16" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="C69" s="17" t="s">
         <v>105</v>
       </c>
       <c r="D69" s="18">
-        <v>6</v>
+        <v>7.79</v>
       </c>
       <c r="E69" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F69" s="19">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="G69" s="20">
-        <v>4887.43</v>
+        <v>5108.01</v>
       </c>
       <c r="H69" s="21">
-        <v>4.8972685738000003E-3</v>
+        <v>4.8716253968999999E-3</v>
       </c>
       <c r="I69" s="20">
-        <v>7.82</v>
+        <v>6.57</v>
       </c>
       <c r="J69" s="15" t="s">
         <v>13</v>
@@ -3223,28 +3309,28 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C70" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="C70" s="17" t="s">
-        <v>107</v>
-      </c>
       <c r="D70" s="18">
-        <v>8.25</v>
+        <v>7.8</v>
       </c>
       <c r="E70" s="17" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F70" s="19">
-        <v>400</v>
+        <v>5000</v>
       </c>
       <c r="G70" s="20">
-        <v>4023.84</v>
+        <v>5098.26</v>
       </c>
       <c r="H70" s="21">
-        <v>4.0319401358000001E-3</v>
+        <v>4.8623265998999996E-3</v>
       </c>
       <c r="I70" s="20">
-        <v>7.71</v>
+        <v>6.57</v>
       </c>
       <c r="J70" s="15" t="s">
         <v>13</v>
@@ -3252,28 +3338,28 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="16" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C71" s="17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D71" s="18">
-        <v>8</v>
+        <v>8.4600000000000009</v>
       </c>
       <c r="E71" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F71" s="19">
-        <v>350</v>
+        <v>50</v>
       </c>
       <c r="G71" s="20">
-        <v>3595.32</v>
+        <v>5080.1000000000004</v>
       </c>
       <c r="H71" s="21">
-        <v>3.6025575095000001E-3</v>
+        <v>4.8450069946000002E-3</v>
       </c>
       <c r="I71" s="20">
-        <v>7.5</v>
+        <v>6.83</v>
       </c>
       <c r="J71" s="15" t="s">
         <v>13</v>
@@ -3281,28 +3367,28 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="16" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="C72" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D72" s="18">
-        <v>9.5399999999999991</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="E72" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F72" s="19">
-        <v>308</v>
+        <v>50</v>
       </c>
       <c r="G72" s="20">
-        <v>3276.05</v>
+        <v>5078.1400000000003</v>
       </c>
       <c r="H72" s="21">
-        <v>3.2826448074000001E-3</v>
+        <v>4.8431376979999998E-3</v>
       </c>
       <c r="I72" s="20">
-        <v>9.4700000000000006</v>
+        <v>6.7</v>
       </c>
       <c r="J72" s="15" t="s">
         <v>13</v>
@@ -3310,28 +3396,28 @@
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="16" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C73" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D73" s="18">
-        <v>9.5399999999999991</v>
+        <v>7.55</v>
       </c>
       <c r="E73" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F73" s="19">
-        <v>308</v>
+        <v>5000</v>
       </c>
       <c r="G73" s="20">
-        <v>3272.41</v>
+        <v>5054.6400000000003</v>
       </c>
       <c r="H73" s="21">
-        <v>3.2789974799999999E-3</v>
+        <v>4.8207252131E-3</v>
       </c>
       <c r="I73" s="20">
-        <v>9.43</v>
+        <v>6.61</v>
       </c>
       <c r="J73" s="15" t="s">
         <v>13</v>
@@ -3339,28 +3425,28 @@
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="16" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="C74" s="17" t="s">
         <v>111</v>
       </c>
       <c r="D74" s="18">
-        <v>9.5399999999999991</v>
+        <v>7.23</v>
       </c>
       <c r="E74" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F74" s="19">
-        <v>308</v>
+        <v>5000</v>
       </c>
       <c r="G74" s="20">
-        <v>3252.7</v>
+        <v>5044.3500000000004</v>
       </c>
       <c r="H74" s="21">
-        <v>3.2592478030000001E-3</v>
+        <v>4.8109114059000004E-3</v>
       </c>
       <c r="I74" s="20">
-        <v>9.2799999999999994</v>
+        <v>6.55</v>
       </c>
       <c r="J74" s="15" t="s">
         <v>13</v>
@@ -3368,28 +3454,28 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C75" s="17" t="s">
         <v>112</v>
       </c>
       <c r="D75" s="18">
-        <v>9.5399999999999991</v>
+        <v>7.54</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F75" s="19">
-        <v>308</v>
+        <v>500</v>
       </c>
       <c r="G75" s="20">
-        <v>3249.21</v>
+        <v>5035.38</v>
       </c>
       <c r="H75" s="21">
-        <v>3.2557507775000001E-3</v>
+        <v>4.8023565128000002E-3</v>
       </c>
       <c r="I75" s="20">
-        <v>9.36</v>
+        <v>6.34</v>
       </c>
       <c r="J75" s="15" t="s">
         <v>13</v>
@@ -3397,28 +3483,28 @@
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="16" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C76" s="17" t="s">
         <v>113</v>
       </c>
       <c r="D76" s="18">
-        <v>9.5399999999999991</v>
+        <v>7.79</v>
       </c>
       <c r="E76" s="17" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F76" s="19">
-        <v>308</v>
+        <v>5000</v>
       </c>
       <c r="G76" s="20">
-        <v>3240.81</v>
+        <v>5024.58</v>
       </c>
       <c r="H76" s="21">
-        <v>3.2473338679999998E-3</v>
+        <v>4.7920563070000003E-3</v>
       </c>
       <c r="I76" s="20">
-        <v>9.4499999999999993</v>
+        <v>6.51</v>
       </c>
       <c r="J76" s="15" t="s">
         <v>13</v>
@@ -3426,28 +3512,28 @@
     </row>
     <row r="77" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="16" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C77" s="17" t="s">
         <v>114</v>
       </c>
       <c r="D77" s="18">
-        <v>9.5399999999999991</v>
+        <v>7.95</v>
       </c>
       <c r="E77" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F77" s="19">
-        <v>308</v>
+        <v>475</v>
       </c>
       <c r="G77" s="20">
-        <v>3229.39</v>
+        <v>4859.4799999999996</v>
       </c>
       <c r="H77" s="21">
-        <v>3.2358908791000002E-3</v>
+        <v>4.6345966791999996E-3</v>
       </c>
       <c r="I77" s="20">
-        <v>9.3000000000000007</v>
+        <v>6.52</v>
       </c>
       <c r="J77" s="15" t="s">
         <v>13</v>
@@ -3455,28 +3541,28 @@
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="16" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D78" s="18">
-        <v>9.5399999999999991</v>
+        <v>8.25</v>
       </c>
       <c r="E78" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F78" s="19">
-        <v>308</v>
+        <v>400</v>
       </c>
       <c r="G78" s="20">
-        <v>3216.3</v>
+        <v>4053.81</v>
       </c>
       <c r="H78" s="21">
-        <v>3.2227745285000001E-3</v>
+        <v>3.8662108628999999E-3</v>
       </c>
       <c r="I78" s="20">
-        <v>9.24</v>
+        <v>6.65</v>
       </c>
       <c r="J78" s="15" t="s">
         <v>13</v>
@@ -3484,28 +3570,28 @@
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="16" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C79" s="17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D79" s="18">
-        <v>9.5399999999999991</v>
+        <v>7.59</v>
       </c>
       <c r="E79" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F79" s="19">
-        <v>308</v>
+        <v>3750</v>
       </c>
       <c r="G79" s="20">
-        <v>3202.02</v>
+        <v>3822.92</v>
       </c>
       <c r="H79" s="21">
-        <v>3.2084657823000001E-3</v>
+        <v>3.6460058147999999E-3</v>
       </c>
       <c r="I79" s="20">
-        <v>9.18</v>
+        <v>6.52</v>
       </c>
       <c r="J79" s="15" t="s">
         <v>13</v>
@@ -3513,28 +3599,28 @@
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="16" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="C80" s="17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D80" s="18">
-        <v>9.5399999999999991</v>
+        <v>7.65</v>
       </c>
       <c r="E80" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F80" s="19">
-        <v>308</v>
+        <v>350</v>
       </c>
       <c r="G80" s="20">
-        <v>3186.44</v>
+        <v>3548.14</v>
       </c>
       <c r="H80" s="21">
-        <v>3.1928544192E-3</v>
+        <v>3.3839418747E-3</v>
       </c>
       <c r="I80" s="20">
-        <v>9.1199999999999992</v>
+        <v>6.71</v>
       </c>
       <c r="J80" s="15" t="s">
         <v>13</v>
@@ -3542,28 +3628,28 @@
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="16" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D81" s="18">
-        <v>9.5399999999999991</v>
+        <v>9.58</v>
       </c>
       <c r="E81" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F81" s="19">
         <v>308</v>
       </c>
       <c r="G81" s="20">
-        <v>3169.48</v>
+        <v>3278.71</v>
       </c>
       <c r="H81" s="21">
-        <v>3.1758602781E-3</v>
+        <v>3.1269803513999999E-3</v>
       </c>
       <c r="I81" s="20">
-        <v>9.0399999999999991</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="J81" s="15" t="s">
         <v>13</v>
@@ -3571,28 +3657,28 @@
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="16" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D82" s="18">
-        <v>7.59</v>
+        <v>9.58</v>
       </c>
       <c r="E82" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F82" s="19">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="G82" s="20">
-        <v>3007.28</v>
+        <v>3262.86</v>
       </c>
       <c r="H82" s="21">
-        <v>3.0133337636000001E-3</v>
+        <v>3.1118638456999999E-3</v>
       </c>
       <c r="I82" s="20">
-        <v>7.49</v>
+        <v>8.93</v>
       </c>
       <c r="J82" s="15" t="s">
         <v>13</v>
@@ -3600,28 +3686,28 @@
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="16" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="C83" s="17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D83" s="18">
-        <v>7.77</v>
+        <v>9.58</v>
       </c>
       <c r="E83" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F83" s="19">
-        <v>2500</v>
+        <v>308</v>
       </c>
       <c r="G83" s="20">
-        <v>2518.21</v>
+        <v>3257.65</v>
       </c>
       <c r="H83" s="21">
-        <v>2.5232792480000001E-3</v>
+        <v>3.1068949501000002E-3</v>
       </c>
       <c r="I83" s="20">
-        <v>7.5</v>
+        <v>8.6300000000000008</v>
       </c>
       <c r="J83" s="15" t="s">
         <v>13</v>
@@ -3629,28 +3715,28 @@
     </row>
     <row r="84" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="16" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D84" s="18">
-        <v>8.0299999999999994</v>
+        <v>9.58</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F84" s="19">
-        <v>250</v>
+        <v>308</v>
       </c>
       <c r="G84" s="20">
-        <v>2509.81</v>
+        <v>3256.35</v>
       </c>
       <c r="H84" s="21">
-        <v>2.5148623384999998E-3</v>
+        <v>3.1056551104999999E-3</v>
       </c>
       <c r="I84" s="20">
-        <v>7.64</v>
+        <v>8.83</v>
       </c>
       <c r="J84" s="15" t="s">
         <v>13</v>
@@ -3658,28 +3744,28 @@
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="16" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="C85" s="17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D85" s="18">
-        <v>7.7</v>
+        <v>9.58</v>
       </c>
       <c r="E85" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F85" s="19">
-        <v>2500</v>
+        <v>308</v>
       </c>
       <c r="G85" s="20">
-        <v>2508.94</v>
+        <v>3253.05</v>
       </c>
       <c r="H85" s="21">
-        <v>2.5139905871999998E-3</v>
+        <v>3.1025078254000001E-3</v>
       </c>
       <c r="I85" s="20">
-        <v>7.52</v>
+        <v>8.81</v>
       </c>
       <c r="J85" s="15" t="s">
         <v>13</v>
@@ -3687,28 +3773,28 @@
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="16" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C86" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D86" s="18">
-        <v>7.77</v>
+        <v>9.58</v>
       </c>
       <c r="E86" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F86" s="19">
-        <v>2500</v>
+        <v>308</v>
       </c>
       <c r="G86" s="20">
-        <v>2505.6999999999998</v>
+        <v>3240.97</v>
       </c>
       <c r="H86" s="21">
-        <v>2.5107440649E-3</v>
+        <v>3.0909868544E-3</v>
       </c>
       <c r="I86" s="20">
-        <v>7.62</v>
+        <v>8.25</v>
       </c>
       <c r="J86" s="15" t="s">
         <v>13</v>
@@ -3716,28 +3802,28 @@
     </row>
     <row r="87" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="16" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="C87" s="17" t="s">
         <v>125</v>
       </c>
       <c r="D87" s="18">
-        <v>8.0400000000000009</v>
+        <v>9.58</v>
       </c>
       <c r="E87" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F87" s="19">
-        <v>250</v>
+        <v>308</v>
       </c>
       <c r="G87" s="20">
-        <v>2501.7399999999998</v>
+        <v>3240.21</v>
       </c>
       <c r="H87" s="21">
-        <v>2.5067760933000002E-3</v>
+        <v>3.0902620251000001E-3</v>
       </c>
       <c r="I87" s="20">
-        <v>7.95</v>
+        <v>7.06</v>
       </c>
       <c r="J87" s="15" t="s">
         <v>13</v>
@@ -3745,28 +3831,28 @@
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="16" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="C88" s="17" t="s">
         <v>126</v>
       </c>
       <c r="D88" s="18">
-        <v>7.7</v>
+        <v>9.58</v>
       </c>
       <c r="E88" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F88" s="19">
-        <v>2500</v>
+        <v>308</v>
       </c>
       <c r="G88" s="20">
-        <v>2499.64</v>
+        <v>3239.95</v>
       </c>
       <c r="H88" s="21">
-        <v>2.5046718659000001E-3</v>
+        <v>3.0900140571999998E-3</v>
       </c>
       <c r="I88" s="20">
-        <v>7.61</v>
+        <v>7.64</v>
       </c>
       <c r="J88" s="15" t="s">
         <v>13</v>
@@ -3774,28 +3860,28 @@
     </row>
     <row r="89" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="16" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="C89" s="17" t="s">
         <v>127</v>
       </c>
       <c r="D89" s="18">
-        <v>7.55</v>
+        <v>9.58</v>
       </c>
       <c r="E89" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F89" s="19">
-        <v>2500</v>
+        <v>308</v>
       </c>
       <c r="G89" s="20">
-        <v>2497.62</v>
+        <v>3239.61</v>
       </c>
       <c r="H89" s="21">
-        <v>2.5026477996000001E-3</v>
+        <v>3.0896897915000002E-3</v>
       </c>
       <c r="I89" s="20">
-        <v>7.62</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="J89" s="15" t="s">
         <v>13</v>
@@ -3803,28 +3889,28 @@
     </row>
     <row r="90" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C90" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="C90" s="17" t="s">
-        <v>129</v>
-      </c>
       <c r="D90" s="18">
-        <v>8.14</v>
+        <v>9.58</v>
       </c>
       <c r="E90" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F90" s="19">
-        <v>2500</v>
+        <v>308</v>
       </c>
       <c r="G90" s="20">
-        <v>2497.06</v>
+        <v>3236.14</v>
       </c>
       <c r="H90" s="21">
-        <v>2.5020866723000001E-3</v>
+        <v>3.0863803735000001E-3</v>
       </c>
       <c r="I90" s="20">
-        <v>8.42</v>
+        <v>8.01</v>
       </c>
       <c r="J90" s="15" t="s">
         <v>13</v>
@@ -3832,28 +3918,28 @@
     </row>
     <row r="91" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="16" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="C91" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D91" s="18">
         <v>7.59</v>
       </c>
       <c r="E91" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F91" s="19">
-        <v>2500</v>
+        <v>300</v>
       </c>
       <c r="G91" s="20">
-        <v>2496.33</v>
+        <v>3071.11</v>
       </c>
       <c r="H91" s="21">
-        <v>2.5013552028000001E-3</v>
+        <v>2.9289875064000001E-3</v>
       </c>
       <c r="I91" s="20">
-        <v>7.75</v>
+        <v>6.56</v>
       </c>
       <c r="J91" s="15" t="s">
         <v>13</v>
@@ -3861,28 +3947,28 @@
     </row>
     <row r="92" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="16" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="C92" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D92" s="18">
-        <v>7.55</v>
+        <v>7.7</v>
       </c>
       <c r="E92" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F92" s="19">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G92" s="20">
-        <v>2496.1799999999998</v>
+        <v>3063.86</v>
       </c>
       <c r="H92" s="21">
-        <v>2.5012049008000001E-3</v>
+        <v>2.9220730164000001E-3</v>
       </c>
       <c r="I92" s="20">
-        <v>7.61</v>
+        <v>6.88</v>
       </c>
       <c r="J92" s="15" t="s">
         <v>13</v>
@@ -3890,28 +3976,28 @@
     </row>
     <row r="93" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="16" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C93" s="17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D93" s="18">
         <v>7.5</v>
       </c>
       <c r="E93" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F93" s="19">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G93" s="20">
-        <v>2494.02</v>
+        <v>3029.39</v>
       </c>
       <c r="H93" s="21">
-        <v>2.4990405527E-3</v>
+        <v>2.8891981927999999E-3</v>
       </c>
       <c r="I93" s="20">
-        <v>7.62</v>
+        <v>6.62</v>
       </c>
       <c r="J93" s="15" t="s">
         <v>13</v>
@@ -3919,28 +4005,28 @@
     </row>
     <row r="94" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="C94" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="C94" s="17" t="s">
-        <v>134</v>
-      </c>
       <c r="D94" s="18">
-        <v>5.78</v>
+        <v>8</v>
       </c>
       <c r="E94" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F94" s="19">
         <v>250</v>
       </c>
       <c r="G94" s="20">
-        <v>2474.62</v>
+        <v>2636.14</v>
       </c>
       <c r="H94" s="21">
-        <v>2.4796014998000001E-3</v>
+        <v>2.5141467172999999E-3</v>
       </c>
       <c r="I94" s="20">
-        <v>7.85</v>
+        <v>7</v>
       </c>
       <c r="J94" s="15" t="s">
         <v>13</v>
@@ -3948,28 +4034,28 @@
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="16" t="s">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="C95" s="17" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D95" s="18">
-        <v>7.1</v>
+        <v>7.97</v>
       </c>
       <c r="E95" s="17" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F95" s="19">
-        <v>200</v>
+        <v>2500</v>
       </c>
       <c r="G95" s="20">
-        <v>1999.4</v>
+        <v>2635.75</v>
       </c>
       <c r="H95" s="21">
-        <v>2.0034248647000001E-3</v>
+        <v>2.5137747654000002E-3</v>
       </c>
       <c r="I95" s="20">
-        <v>7.3</v>
+        <v>7.03</v>
       </c>
       <c r="J95" s="15" t="s">
         <v>13</v>
@@ -3977,28 +4063,28 @@
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="16" t="s">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="C96" s="17" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D96" s="18">
         <v>7.84</v>
       </c>
       <c r="E96" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F96" s="19">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="G96" s="20">
-        <v>1996.41</v>
+        <v>2609.69</v>
       </c>
       <c r="H96" s="21">
-        <v>2.0004288456999999E-3</v>
+        <v>2.4889207503E-3</v>
       </c>
       <c r="I96" s="20">
-        <v>7.92</v>
+        <v>7.06</v>
       </c>
       <c r="J96" s="15" t="s">
         <v>13</v>
@@ -4006,28 +4092,28 @@
     </row>
     <row r="97" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="16" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="C97" s="17" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D97" s="18">
-        <v>7.79</v>
+        <v>7.8</v>
       </c>
       <c r="E97" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F97" s="19">
-        <v>1500</v>
+        <v>250</v>
       </c>
       <c r="G97" s="20">
-        <v>1508.02</v>
+        <v>2609.66</v>
       </c>
       <c r="H97" s="21">
-        <v>1.5110556989E-3</v>
+        <v>2.4888921385999999E-3</v>
       </c>
       <c r="I97" s="20">
-        <v>7.52</v>
+        <v>7</v>
       </c>
       <c r="J97" s="15" t="s">
         <v>13</v>
@@ -4035,28 +4121,28 @@
     </row>
     <row r="98" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="16" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C98" s="17" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D98" s="18">
-        <v>7.63</v>
+        <v>7.75</v>
       </c>
       <c r="E98" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F98" s="19">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="G98" s="20">
-        <v>1499.19</v>
+        <v>2555.7399999999998</v>
       </c>
       <c r="H98" s="21">
-        <v>1.5022079238E-3</v>
+        <v>2.4374674074E-3</v>
       </c>
       <c r="I98" s="20">
-        <v>7.62</v>
+        <v>6.52</v>
       </c>
       <c r="J98" s="15" t="s">
         <v>13</v>
@@ -4064,28 +4150,28 @@
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="16" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="C99" s="17" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D99" s="18">
-        <v>7.44</v>
+        <v>8.4600000000000009</v>
       </c>
       <c r="E99" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F99" s="19">
-        <v>1500</v>
+        <v>25</v>
       </c>
       <c r="G99" s="20">
-        <v>1498.67</v>
+        <v>2539.3000000000002</v>
       </c>
       <c r="H99" s="21">
-        <v>1.5016868770000001E-3</v>
+        <v>2.4217882052E-3</v>
       </c>
       <c r="I99" s="20">
-        <v>7.47</v>
+        <v>6.83</v>
       </c>
       <c r="J99" s="15" t="s">
         <v>13</v>
@@ -4093,28 +4179,28 @@
     </row>
     <row r="100" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="16" t="s">
-        <v>45</v>
+        <v>139</v>
       </c>
       <c r="C100" s="17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D100" s="18">
-        <v>7.52</v>
+        <v>7.7120000000000006</v>
       </c>
       <c r="E100" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F100" s="19">
-        <v>150</v>
+        <v>2500</v>
       </c>
       <c r="G100" s="20">
-        <v>1498.08</v>
+        <v>2534.8000000000002</v>
       </c>
       <c r="H100" s="21">
-        <v>1.5010956892999999E-3</v>
+        <v>2.4174964528000001E-3</v>
       </c>
       <c r="I100" s="20">
-        <v>7.59</v>
+        <v>7.09</v>
       </c>
       <c r="J100" s="15" t="s">
         <v>13</v>
@@ -4122,28 +4208,28 @@
     </row>
     <row r="101" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="16" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C101" s="17" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D101" s="18">
-        <v>8.11</v>
+        <v>7.54</v>
       </c>
       <c r="E101" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F101" s="19">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="G101" s="20">
-        <v>1251.8599999999999</v>
+        <v>2534.62</v>
       </c>
       <c r="H101" s="21">
-        <v>1.2543800395000001E-3</v>
+        <v>2.4173247827000001E-3</v>
       </c>
       <c r="I101" s="20">
-        <v>7.72</v>
+        <v>6.55</v>
       </c>
       <c r="J101" s="15" t="s">
         <v>13</v>
@@ -4151,28 +4237,28 @@
     </row>
     <row r="102" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="16" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C102" s="17" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D102" s="18">
-        <v>7.15</v>
+        <v>7.77</v>
       </c>
       <c r="E102" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F102" s="19">
-        <v>100</v>
+        <v>2500</v>
       </c>
       <c r="G102" s="20">
-        <v>995.11</v>
+        <v>2532.19</v>
       </c>
       <c r="H102" s="21">
-        <v>9.9711319250000009E-4</v>
+        <v>2.4150072364000001E-3</v>
       </c>
       <c r="I102" s="20">
-        <v>7.78</v>
+        <v>6.55</v>
       </c>
       <c r="J102" s="15" t="s">
         <v>13</v>
@@ -4180,28 +4266,28 @@
     </row>
     <row r="103" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="16" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C103" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D103" s="18">
-        <v>8.75</v>
+        <v>7.7</v>
       </c>
       <c r="E103" s="17" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F103" s="19">
-        <v>50</v>
+        <v>2500</v>
       </c>
       <c r="G103" s="20">
-        <v>501.25</v>
+        <v>2531.52</v>
       </c>
       <c r="H103" s="21">
-        <v>5.0225903440000001E-4</v>
+        <v>2.4143682420999998E-3</v>
       </c>
       <c r="I103" s="20">
-        <v>7.79</v>
+        <v>6.55</v>
       </c>
       <c r="J103" s="15" t="s">
         <v>13</v>
@@ -4209,28 +4295,28 @@
     </row>
     <row r="104" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="16" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="C104" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D104" s="18">
-        <v>7.5</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="E104" s="17" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F104" s="19">
-        <v>25</v>
+        <v>250</v>
       </c>
       <c r="G104" s="20">
-        <v>249.32</v>
+        <v>2531.1</v>
       </c>
       <c r="H104" s="21">
-        <v>2.4982189019999998E-4</v>
+        <v>2.4139676785999999E-3</v>
       </c>
       <c r="I104" s="20">
-        <v>7.75</v>
+        <v>6.55</v>
       </c>
       <c r="J104" s="15" t="s">
         <v>13</v>
@@ -4238,36 +4324,57 @@
     </row>
     <row r="105" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B105" s="16" t="s">
-        <v>13</v>
+        <v>59</v>
+      </c>
+      <c r="C105" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="D105" s="18">
+        <v>7.63</v>
+      </c>
+      <c r="E105" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F105" s="19">
+        <v>250</v>
+      </c>
+      <c r="G105" s="20">
+        <v>2529.31</v>
+      </c>
+      <c r="H105" s="21">
+        <v>2.4122605148000002E-3</v>
+      </c>
+      <c r="I105" s="20">
+        <v>6.55</v>
       </c>
       <c r="J105" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="106" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="11" t="s">
+      <c r="B106" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C106" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="C106" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D106" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E106" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F106" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G106" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="H106" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="I106" s="13" t="s">
-        <v>13</v>
+      <c r="D106" s="18">
+        <v>7.55</v>
+      </c>
+      <c r="E106" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F106" s="19">
+        <v>2500</v>
+      </c>
+      <c r="G106" s="20">
+        <v>2526.59</v>
+      </c>
+      <c r="H106" s="21">
+        <v>2.4096663888999999E-3</v>
+      </c>
+      <c r="I106" s="20">
+        <v>6.55</v>
       </c>
       <c r="J106" s="15" t="s">
         <v>13</v>
@@ -4275,36 +4382,57 @@
     </row>
     <row r="107" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B107" s="16" t="s">
-        <v>13</v>
+        <v>110</v>
+      </c>
+      <c r="C107" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="D107" s="18">
+        <v>7.51</v>
+      </c>
+      <c r="E107" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F107" s="19">
+        <v>2500</v>
+      </c>
+      <c r="G107" s="20">
+        <v>2520.66</v>
+      </c>
+      <c r="H107" s="21">
+        <v>2.404010813E-3</v>
+      </c>
+      <c r="I107" s="20">
+        <v>6.5</v>
       </c>
       <c r="J107" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="108" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B108" s="11" t="s">
+      <c r="B108" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C108" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="C108" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D108" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E108" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F108" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G108" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="H108" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="I108" s="13" t="s">
-        <v>13</v>
+      <c r="D108" s="18">
+        <v>7.59</v>
+      </c>
+      <c r="E108" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F108" s="19">
+        <v>2500</v>
+      </c>
+      <c r="G108" s="20">
+        <v>2515.2600000000002</v>
+      </c>
+      <c r="H108" s="21">
+        <v>2.3988607101000001E-3</v>
+      </c>
+      <c r="I108" s="20">
+        <v>6.6</v>
       </c>
       <c r="J108" s="15" t="s">
         <v>13</v>
@@ -4312,36 +4440,57 @@
     </row>
     <row r="109" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B109" s="16" t="s">
-        <v>13</v>
+        <v>59</v>
+      </c>
+      <c r="C109" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="D109" s="18">
+        <v>6.35</v>
+      </c>
+      <c r="E109" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F109" s="19">
+        <v>625</v>
+      </c>
+      <c r="G109" s="20">
+        <v>2494.58</v>
+      </c>
+      <c r="H109" s="21">
+        <v>2.3791377234E-3</v>
+      </c>
+      <c r="I109" s="20">
+        <v>6.55</v>
       </c>
       <c r="J109" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="110" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B110" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="C110" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D110" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E110" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F110" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G110" s="13">
-        <v>27735.38</v>
-      </c>
-      <c r="H110" s="14">
-        <v>2.7791212325399998E-2</v>
-      </c>
-      <c r="I110" s="13" t="s">
-        <v>13</v>
+      <c r="B110" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="C110" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="D110" s="18">
+        <v>7.48</v>
+      </c>
+      <c r="E110" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F110" s="19">
+        <v>2500</v>
+      </c>
+      <c r="G110" s="20">
+        <v>2480.19</v>
+      </c>
+      <c r="H110" s="21">
+        <v>2.3654136528999999E-3</v>
+      </c>
+      <c r="I110" s="20">
+        <v>7.82</v>
       </c>
       <c r="J110" s="15" t="s">
         <v>13</v>
@@ -4349,28 +4498,28 @@
     </row>
     <row r="111" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B111" s="16" t="s">
-        <v>150</v>
+        <v>51</v>
       </c>
       <c r="C111" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="D111" s="17" t="s">
-        <v>13</v>
+        <v>152</v>
+      </c>
+      <c r="D111" s="18">
+        <v>7.83</v>
       </c>
       <c r="E111" s="17" t="s">
-        <v>152</v>
+        <v>37</v>
       </c>
       <c r="F111" s="19">
-        <v>83</v>
+        <v>1500</v>
       </c>
       <c r="G111" s="20">
-        <v>8174.44</v>
+        <v>1555.11</v>
       </c>
       <c r="H111" s="21">
-        <v>8.1908954441E-3</v>
+        <v>1.4831438016999999E-3</v>
       </c>
       <c r="I111" s="20">
-        <v>8.32</v>
+        <v>6.59</v>
       </c>
       <c r="J111" s="15" t="s">
         <v>13</v>
@@ -4378,28 +4527,28 @@
     </row>
     <row r="112" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" s="16" t="s">
-        <v>150</v>
+        <v>57</v>
       </c>
       <c r="C112" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="D112" s="17" t="s">
-        <v>13</v>
+      <c r="D112" s="18">
+        <v>7.52</v>
       </c>
       <c r="E112" s="17" t="s">
-        <v>152</v>
+        <v>37</v>
       </c>
       <c r="F112" s="19">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="G112" s="20">
-        <v>6214.47</v>
+        <v>1518.64</v>
       </c>
       <c r="H112" s="21">
-        <v>6.2269799534000001E-3</v>
+        <v>1.4483615327E-3</v>
       </c>
       <c r="I112" s="20">
-        <v>8.34</v>
+        <v>6.55</v>
       </c>
       <c r="J112" s="15" t="s">
         <v>13</v>
@@ -4407,28 +4556,28 @@
     </row>
     <row r="113" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B113" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C113" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="D113" s="18">
+        <v>6.45</v>
+      </c>
+      <c r="E113" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F113" s="19">
         <v>150</v>
       </c>
-      <c r="C113" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="D113" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E113" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="F113" s="19">
-        <v>40</v>
-      </c>
       <c r="G113" s="20">
-        <v>3825.82</v>
+        <v>1487.56</v>
       </c>
       <c r="H113" s="21">
-        <v>3.8335215143999999E-3</v>
+        <v>1.4187198292999999E-3</v>
       </c>
       <c r="I113" s="20">
-        <v>8.34</v>
+        <v>6.76</v>
       </c>
       <c r="J113" s="15" t="s">
         <v>13</v>
@@ -4436,28 +4585,28 @@
     </row>
     <row r="114" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B114" s="16" t="s">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="C114" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D114" s="17" t="s">
-        <v>13</v>
+      <c r="D114" s="18">
+        <v>7.68</v>
       </c>
       <c r="E114" s="17" t="s">
-        <v>157</v>
+        <v>37</v>
       </c>
       <c r="F114" s="19">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="G114" s="20">
-        <v>3253.4</v>
+        <v>507.53</v>
       </c>
       <c r="H114" s="21">
-        <v>3.2599492121000002E-3</v>
+        <v>4.840429125E-4</v>
       </c>
       <c r="I114" s="20">
-        <v>8.35</v>
+        <v>6.55</v>
       </c>
       <c r="J114" s="15" t="s">
         <v>13</v>
@@ -4465,28 +4614,28 @@
     </row>
     <row r="115" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" s="16" t="s">
-        <v>155</v>
+        <v>57</v>
       </c>
       <c r="C115" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D115" s="17" t="s">
-        <v>13</v>
+        <v>157</v>
+      </c>
+      <c r="D115" s="18">
+        <v>8.75</v>
       </c>
       <c r="E115" s="17" t="s">
-        <v>157</v>
+        <v>37</v>
       </c>
       <c r="F115" s="19">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="G115" s="20">
-        <v>3176.6</v>
+        <v>501.05</v>
       </c>
       <c r="H115" s="21">
-        <v>3.1829946109E-3</v>
+        <v>4.77862789E-4</v>
       </c>
       <c r="I115" s="20">
-        <v>8.41</v>
+        <v>6.38</v>
       </c>
       <c r="J115" s="15" t="s">
         <v>13</v>
@@ -4494,28 +4643,28 @@
     </row>
     <row r="116" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B116" s="16" t="s">
-        <v>155</v>
+        <v>45</v>
       </c>
       <c r="C116" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="D116" s="17" t="s">
-        <v>13</v>
+        <v>158</v>
+      </c>
+      <c r="D116" s="18">
+        <v>7.49</v>
       </c>
       <c r="E116" s="17" t="s">
-        <v>157</v>
+        <v>37</v>
       </c>
       <c r="F116" s="19">
-        <v>31</v>
+        <v>360</v>
       </c>
       <c r="G116" s="20">
-        <v>3090.65</v>
+        <v>363.76</v>
       </c>
       <c r="H116" s="21">
-        <v>3.0968715905000002E-3</v>
+        <v>3.4692619120000001E-4</v>
       </c>
       <c r="I116" s="20">
-        <v>8.41</v>
+        <v>6.63</v>
       </c>
       <c r="J116" s="15" t="s">
         <v>13</v>
@@ -4531,25 +4680,25 @@
     </row>
     <row r="118" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B118" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C118" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D118" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E118" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F118" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G118" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="C118" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D118" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E118" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F118" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G118" s="13" t="s">
-        <v>147</v>
-      </c>
       <c r="H118" s="14" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="I118" s="13" t="s">
         <v>13</v>
@@ -4583,10 +4732,10 @@
         <v>13</v>
       </c>
       <c r="G120" s="13" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="H120" s="14" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="I120" s="13" t="s">
         <v>13</v>
@@ -4619,11 +4768,11 @@
       <c r="F122" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="G122" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="H122" s="14" t="s">
-        <v>147</v>
+      <c r="G122" s="13">
+        <v>25039.190000000002</v>
+      </c>
+      <c r="H122" s="14">
+        <v>2.3880445402599999E-2</v>
       </c>
       <c r="I122" s="13" t="s">
         <v>13</v>
@@ -4634,36 +4783,57 @@
     </row>
     <row r="123" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B123" s="16" t="s">
-        <v>13</v>
+        <v>163</v>
+      </c>
+      <c r="C123" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="D123" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E123" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="F123" s="19">
+        <v>83</v>
+      </c>
+      <c r="G123" s="20">
+        <v>8076.92</v>
+      </c>
+      <c r="H123" s="21">
+        <v>7.7031424371999998E-3</v>
+      </c>
+      <c r="I123" s="20">
+        <v>7.76</v>
       </c>
       <c r="J123" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="124" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="11" t="s">
+      <c r="B124" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="C124" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D124" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E124" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F124" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G124" s="13">
-        <v>44625.880000000005</v>
-      </c>
-      <c r="H124" s="14">
-        <v>4.4715713514499995E-2</v>
-      </c>
-      <c r="I124" s="13" t="s">
-        <v>13</v>
+      <c r="C124" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="D124" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E124" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="F124" s="19">
+        <v>77</v>
+      </c>
+      <c r="G124" s="20">
+        <v>4709.1099999999997</v>
+      </c>
+      <c r="H124" s="21">
+        <v>4.4911853878000004E-3</v>
+      </c>
+      <c r="I124" s="20">
+        <v>7.39</v>
       </c>
       <c r="J124" s="15" t="s">
         <v>13</v>
@@ -4671,36 +4841,57 @@
     </row>
     <row r="125" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B125" s="16" t="s">
-        <v>13</v>
+        <v>163</v>
+      </c>
+      <c r="C125" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="D125" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E125" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="F125" s="19">
+        <v>40</v>
+      </c>
+      <c r="G125" s="20">
+        <v>3669.08</v>
+      </c>
+      <c r="H125" s="21">
+        <v>3.4992851053999999E-3</v>
+      </c>
+      <c r="I125" s="20">
+        <v>7.52</v>
       </c>
       <c r="J125" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="126" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="C126" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D126" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E126" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F126" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G126" s="13">
-        <v>39974.11</v>
-      </c>
-      <c r="H126" s="14">
-        <v>4.0054579332799996E-2</v>
-      </c>
-      <c r="I126" s="13" t="s">
-        <v>13</v>
+      <c r="B126" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="C126" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="D126" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E126" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="F126" s="19">
+        <v>31</v>
+      </c>
+      <c r="G126" s="20">
+        <v>3088.84</v>
+      </c>
+      <c r="H126" s="21">
+        <v>2.9458970108999999E-3</v>
+      </c>
+      <c r="I126" s="20">
+        <v>7.76</v>
       </c>
       <c r="J126" s="15" t="s">
         <v>13</v>
@@ -4708,28 +4899,28 @@
     </row>
     <row r="127" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" s="16" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C127" s="17" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D127" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E127" s="17" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F127" s="19">
-        <v>2500</v>
+        <v>33</v>
       </c>
       <c r="G127" s="20">
-        <v>11669.78</v>
+        <v>2944.31</v>
       </c>
       <c r="H127" s="21">
-        <v>1.1693271690299999E-2</v>
+        <v>2.8080554604000001E-3</v>
       </c>
       <c r="I127" s="20">
-        <v>7.62</v>
+        <v>7.58</v>
       </c>
       <c r="J127" s="15" t="s">
         <v>13</v>
@@ -4737,28 +4928,28 @@
     </row>
     <row r="128" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B128" s="16" t="s">
-        <v>64</v>
+        <v>168</v>
       </c>
       <c r="C128" s="17" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D128" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E128" s="17" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F128" s="19">
-        <v>2000</v>
+        <v>36</v>
       </c>
       <c r="G128" s="20">
-        <v>9334.19</v>
+        <v>2550.9299999999998</v>
       </c>
       <c r="H128" s="21">
-        <v>9.3529800628999998E-3</v>
+        <v>2.4328800008999998E-3</v>
       </c>
       <c r="I128" s="20">
-        <v>7.64</v>
+        <v>7.39</v>
       </c>
       <c r="J128" s="15" t="s">
         <v>13</v>
@@ -4766,57 +4957,36 @@
     </row>
     <row r="129" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B129" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C129" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="D129" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E129" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="F129" s="19">
-        <v>1500</v>
-      </c>
-      <c r="G129" s="20">
-        <v>7107.38</v>
-      </c>
-      <c r="H129" s="21">
-        <v>7.1216874136000004E-3</v>
-      </c>
-      <c r="I129" s="20">
-        <v>7.64</v>
+        <v>13</v>
       </c>
       <c r="J129" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="130" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B130" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="C130" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="D130" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E130" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="F130" s="19">
-        <v>1500</v>
-      </c>
-      <c r="G130" s="20">
-        <v>7029.54</v>
-      </c>
-      <c r="H130" s="21">
-        <v>7.0436907189000003E-3</v>
-      </c>
-      <c r="I130" s="20">
-        <v>7.63</v>
+      <c r="B130" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C130" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D130" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E130" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F130" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G130" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="H130" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="I130" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="J130" s="15" t="s">
         <v>13</v>
@@ -4824,35 +4994,35 @@
     </row>
     <row r="131" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B131" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C131" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="D131" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E131" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="F131" s="19">
-        <v>1000</v>
-      </c>
-      <c r="G131" s="20">
-        <v>4833.22</v>
-      </c>
-      <c r="H131" s="21">
-        <v>4.8429494471000003E-3</v>
-      </c>
-      <c r="I131" s="20">
-        <v>7.68</v>
+        <v>13</v>
       </c>
       <c r="J131" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="132" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B132" s="16" t="s">
+      <c r="B132" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="C132" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D132" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E132" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F132" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G132" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="H132" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="I132" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J132" s="15" t="s">
@@ -4860,28 +5030,7 @@
       </c>
     </row>
     <row r="133" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B133" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="C133" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D133" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E133" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F133" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G133" s="13">
-        <v>4651.7700000000004</v>
-      </c>
-      <c r="H133" s="14">
-        <v>4.6611341816999996E-3</v>
-      </c>
-      <c r="I133" s="13" t="s">
+      <c r="B133" s="16" t="s">
         <v>13</v>
       </c>
       <c r="J133" s="15" t="s">
@@ -4889,29 +5038,29 @@
       </c>
     </row>
     <row r="134" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B134" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="C134" s="17" t="s">
+      <c r="B134" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="D134" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E134" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="F134" s="19">
-        <v>1000</v>
-      </c>
-      <c r="G134" s="20">
-        <v>4651.7700000000004</v>
-      </c>
-      <c r="H134" s="21">
-        <v>4.6611341816999996E-3</v>
-      </c>
-      <c r="I134" s="20">
-        <v>7.59</v>
+      <c r="C134" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D134" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E134" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F134" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G134" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="H134" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="I134" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="J134" s="15" t="s">
         <v>13</v>
@@ -4941,11 +5090,11 @@
       <c r="F136" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="G136" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="H136" s="14" t="s">
-        <v>147</v>
+      <c r="G136" s="13">
+        <v>9494.0600000000013</v>
+      </c>
+      <c r="H136" s="14">
+        <v>9.054701109600001E-3</v>
       </c>
       <c r="I136" s="13" t="s">
         <v>13</v>
@@ -4978,11 +5127,11 @@
       <c r="F138" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="G138" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="H138" s="14" t="s">
-        <v>147</v>
+      <c r="G138" s="13">
+        <v>9494.0600000000013</v>
+      </c>
+      <c r="H138" s="14">
+        <v>9.054701109600001E-3</v>
       </c>
       <c r="I138" s="13" t="s">
         <v>13</v>
@@ -4993,36 +5142,57 @@
     </row>
     <row r="139" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B139" s="16" t="s">
-        <v>13</v>
+        <v>178</v>
+      </c>
+      <c r="C139" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="D139" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E139" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="F139" s="19">
+        <v>1000</v>
+      </c>
+      <c r="G139" s="20">
+        <v>4692.34</v>
+      </c>
+      <c r="H139" s="21">
+        <v>4.4751914571000001E-3</v>
+      </c>
+      <c r="I139" s="20">
+        <v>6.69</v>
       </c>
       <c r="J139" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="140" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B140" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="C140" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D140" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E140" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F140" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G140" s="13">
-        <v>2661.5</v>
-      </c>
-      <c r="H140" s="14">
-        <v>2.6668576960000002E-3</v>
-      </c>
-      <c r="I140" s="13" t="s">
-        <v>13</v>
+      <c r="B140" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="C140" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="D140" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E140" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="F140" s="19">
+        <v>500</v>
+      </c>
+      <c r="G140" s="20">
+        <v>2406.6</v>
+      </c>
+      <c r="H140" s="21">
+        <v>2.2952291949E-3</v>
+      </c>
+      <c r="I140" s="20">
+        <v>6.41</v>
       </c>
       <c r="J140" s="15" t="s">
         <v>13</v>
@@ -5030,28 +5200,28 @@
     </row>
     <row r="141" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B141" s="16" t="s">
-        <v>179</v>
+        <v>95</v>
       </c>
       <c r="C141" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="D141" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E141" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="D141" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E141" s="17" t="s">
-        <v>181</v>
-      </c>
       <c r="F141" s="19">
-        <v>24393.734</v>
+        <v>500</v>
       </c>
       <c r="G141" s="20">
-        <v>2661.5</v>
+        <v>2395.12</v>
       </c>
       <c r="H141" s="21">
-        <v>2.6668576960000002E-3</v>
-      </c>
-      <c r="I141" s="20" t="s">
-        <v>13</v>
+        <v>2.2842804576000001E-3</v>
+      </c>
+      <c r="I141" s="20">
+        <v>6.45</v>
       </c>
       <c r="J141" s="15" t="s">
         <v>13</v>
@@ -5067,7 +5237,7 @@
     </row>
     <row r="143" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B143" s="11" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C143" s="12" t="s">
         <v>13</v>
@@ -5081,11 +5251,11 @@
       <c r="F143" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="G143" s="13">
-        <v>5659.64</v>
-      </c>
-      <c r="H143" s="14">
-        <v>5.6710330604999998E-3</v>
+      <c r="G143" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="H143" s="14" t="s">
+        <v>160</v>
       </c>
       <c r="I143" s="13" t="s">
         <v>13</v>
@@ -5103,184 +5273,866 @@
       </c>
     </row>
     <row r="145" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B145" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="C145" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D145" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E145" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F145" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G145" s="23">
-        <v>30082.027908810414</v>
-      </c>
-      <c r="H145" s="24">
-        <v>3.0142584121919377E-2</v>
-      </c>
-      <c r="I145" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J145" s="25" t="s">
+      <c r="B145" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="C145" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D145" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E145" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F145" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G145" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="H145" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="I145" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J145" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="146" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B146" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="C146" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="D146" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E146" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F146" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G146" s="23">
-        <v>997991.00790881005</v>
-      </c>
-      <c r="H146" s="24">
-        <v>0.9999999999946193</v>
-      </c>
-      <c r="I146" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J146" s="25" t="s">
+      <c r="B146" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J146" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="147" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B147" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C147" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D147" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E147" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F147" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G147" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="H147" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="I147" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J147" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="148" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B148" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J148" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="149" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B149" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C149" s="5"/>
-      <c r="D149" s="5"/>
-      <c r="E149" s="5"/>
-      <c r="F149" s="5"/>
-      <c r="G149" s="5"/>
-      <c r="H149" s="5"/>
-      <c r="I149" s="5"/>
+      <c r="B149" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="C149" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D149" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E149" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F149" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G149" s="13">
+        <v>2729.89</v>
+      </c>
+      <c r="H149" s="14">
+        <v>2.6035582261E-3</v>
+      </c>
+      <c r="I149" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J149" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="150" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B150" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="C150" s="5"/>
-      <c r="D150" s="5"/>
-      <c r="E150" s="5"/>
-      <c r="F150" s="5"/>
-      <c r="G150" s="5"/>
-      <c r="H150" s="5"/>
+      <c r="B150" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="C150" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="D150" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E150" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="F150" s="19">
+        <v>24393.734</v>
+      </c>
+      <c r="G150" s="20">
+        <v>2729.89</v>
+      </c>
+      <c r="H150" s="21">
+        <v>2.6035582261E-3</v>
+      </c>
+      <c r="I150" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="J150" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="151" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B151" s="17" t="s">
+      <c r="B151" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J151" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="152" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B152" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="C152" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D152" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E152" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F152" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G152" s="13">
+        <v>13382.06</v>
+      </c>
+      <c r="H152" s="14">
+        <v>1.2762775201800001E-2</v>
+      </c>
+      <c r="I152" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J152" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="153" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B153" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J153" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="154" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B154" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="C154" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D154" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E154" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F154" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G154" s="24">
+        <v>33202.558066099999</v>
+      </c>
+      <c r="H154" s="25">
+        <v>3.1666035328274278E-2</v>
+      </c>
+      <c r="I154" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="J154" s="26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="155" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B155" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="C155" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D155" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E155" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F155" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G155" s="24">
+        <v>1048522.7380661</v>
+      </c>
+      <c r="H155" s="25">
+        <v>0.99999999999397449</v>
+      </c>
+      <c r="I155" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="J155" s="26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="156" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B156" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C156" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D156" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E156" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F156" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G156" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H156" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="I156" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="J156" s="26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="157" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B157" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="C157" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D157" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E157" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F157" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G157" s="24">
+        <v>-110000</v>
+      </c>
+      <c r="H157" s="25">
+        <v>-0.10490950363449868</v>
+      </c>
+      <c r="I157" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="J157" s="26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="158" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B158" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="C158" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D158" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E158" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F158" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G158" s="20">
+        <v>-7500</v>
+      </c>
+      <c r="H158" s="21">
+        <v>-7.1529207023521809E-3</v>
+      </c>
+      <c r="I158" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J158" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="159" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B159" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="C159" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D159" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E159" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F159" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G159" s="20">
+        <v>-7500</v>
+      </c>
+      <c r="H159" s="21">
+        <v>-7.1529207023521809E-3</v>
+      </c>
+      <c r="I159" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J159" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="160" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B160" s="16" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="152" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B152" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="C152" s="5"/>
-      <c r="D152" s="5"/>
-      <c r="E152" s="5"/>
-      <c r="F152" s="5"/>
-      <c r="G152" s="5"/>
-      <c r="H152" s="5"/>
-    </row>
-    <row r="153" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B153" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="C153" s="5"/>
-      <c r="D153" s="5"/>
-      <c r="E153" s="5"/>
-      <c r="F153" s="5"/>
-      <c r="G153" s="5"/>
-      <c r="H153" s="5"/>
-    </row>
-    <row r="154" spans="2:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B154" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="C154" s="5"/>
-      <c r="D154" s="5"/>
-      <c r="E154" s="5"/>
-      <c r="F154" s="5"/>
-      <c r="G154" s="5"/>
-      <c r="H154" s="5"/>
-    </row>
-    <row r="155" spans="2:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B155" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="C155" s="5"/>
-      <c r="D155" s="5"/>
-      <c r="E155" s="5"/>
-      <c r="F155" s="5"/>
-      <c r="G155" s="5"/>
-      <c r="H155" s="5"/>
-    </row>
-    <row r="156" spans="2:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B156" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="C156" s="5"/>
-      <c r="D156" s="5"/>
-      <c r="E156" s="5"/>
-      <c r="F156" s="5"/>
-      <c r="G156" s="5"/>
-      <c r="H156" s="5"/>
-    </row>
-    <row r="157" spans="2:10" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B157" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="C157" s="7"/>
-      <c r="D157" s="7"/>
-      <c r="E157" s="7"/>
-      <c r="F157" s="7"/>
-      <c r="G157" s="7"/>
-    </row>
-    <row r="160" spans="2:10" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B160" s="26" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="175" spans="2:2" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B175" s="26" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="176" spans="2:2" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="B176" s="26" t="s">
-        <v>195</v>
+      <c r="C160" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D160" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E160" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F160" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G160" s="20">
+        <v>-2500</v>
+      </c>
+      <c r="H160" s="21">
+        <v>-2.3843069007840603E-3</v>
+      </c>
+      <c r="I160" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J160" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="161" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B161" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="C161" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D161" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E161" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F161" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G161" s="20">
+        <v>-10000</v>
+      </c>
+      <c r="H161" s="21">
+        <v>-9.5372276031362412E-3</v>
+      </c>
+      <c r="I161" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J161" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="162" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B162" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="C162" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D162" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E162" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F162" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G162" s="20">
+        <v>-10000</v>
+      </c>
+      <c r="H162" s="21">
+        <v>-9.5372276031362412E-3</v>
+      </c>
+      <c r="I162" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J162" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="163" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B163" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="C163" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D163" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E163" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F163" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G163" s="20">
+        <v>-5000</v>
+      </c>
+      <c r="H163" s="21">
+        <v>-4.7686138015681206E-3</v>
+      </c>
+      <c r="I163" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J163" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="164" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B164" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="C164" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D164" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E164" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F164" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G164" s="20">
+        <v>-10000</v>
+      </c>
+      <c r="H164" s="21">
+        <v>-9.5372276031362412E-3</v>
+      </c>
+      <c r="I164" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J164" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="165" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B165" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="C165" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D165" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E165" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F165" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G165" s="20">
+        <v>-10000</v>
+      </c>
+      <c r="H165" s="21">
+        <v>-9.5372276031362412E-3</v>
+      </c>
+      <c r="I165" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J165" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="166" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B166" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="C166" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D166" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E166" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F166" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G166" s="20">
+        <v>-10000</v>
+      </c>
+      <c r="H166" s="21">
+        <v>-9.5372276031362412E-3</v>
+      </c>
+      <c r="I166" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J166" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="167" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B167" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="C167" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D167" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E167" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F167" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G167" s="20">
+        <v>-2500</v>
+      </c>
+      <c r="H167" s="21">
+        <v>-2.3843069007840603E-3</v>
+      </c>
+      <c r="I167" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J167" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="168" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B168" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="C168" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D168" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E168" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F168" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G168" s="20">
+        <v>-10000</v>
+      </c>
+      <c r="H168" s="21">
+        <v>-9.5372276031362412E-3</v>
+      </c>
+      <c r="I168" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J168" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="169" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B169" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="C169" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D169" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E169" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F169" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G169" s="20">
+        <v>-10000</v>
+      </c>
+      <c r="H169" s="21">
+        <v>-9.5372276031362412E-3</v>
+      </c>
+      <c r="I169" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J169" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="170" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B170" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="C170" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D170" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E170" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F170" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G170" s="20">
+        <v>-10000</v>
+      </c>
+      <c r="H170" s="21">
+        <v>-9.5372276031362412E-3</v>
+      </c>
+      <c r="I170" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J170" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="171" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B171" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="C171" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D171" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E171" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F171" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G171" s="20">
+        <v>-5000</v>
+      </c>
+      <c r="H171" s="21">
+        <v>-4.7686138015681206E-3</v>
+      </c>
+      <c r="I171" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J171" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="172" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B172" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C172" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D172" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="E172" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F172" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="G172" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H172" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="I172" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="J172" s="27" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="175" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B175" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C175" s="3"/>
+      <c r="D175" s="3"/>
+      <c r="E175" s="3"/>
+      <c r="F175" s="3"/>
+      <c r="G175" s="3"/>
+      <c r="H175" s="3"/>
+      <c r="I175" s="3"/>
+    </row>
+    <row r="176" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B176" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C176" s="3"/>
+      <c r="D176" s="3"/>
+      <c r="E176" s="3"/>
+      <c r="F176" s="3"/>
+      <c r="G176" s="3"/>
+      <c r="H176" s="3"/>
+    </row>
+    <row r="177" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B177" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C177" s="3"/>
+      <c r="D177" s="3"/>
+      <c r="E177" s="3"/>
+      <c r="F177" s="3"/>
+      <c r="G177" s="3"/>
+      <c r="H177" s="3"/>
+    </row>
+    <row r="178" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B178" s="17" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="179" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B179" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C179" s="3"/>
+      <c r="D179" s="3"/>
+      <c r="E179" s="3"/>
+      <c r="F179" s="3"/>
+      <c r="G179" s="3"/>
+      <c r="H179" s="3"/>
+    </row>
+    <row r="180" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B180" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C180" s="3"/>
+      <c r="D180" s="3"/>
+      <c r="E180" s="3"/>
+      <c r="F180" s="3"/>
+      <c r="G180" s="3"/>
+      <c r="H180" s="3"/>
+    </row>
+    <row r="181" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B181" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C181" s="3"/>
+      <c r="D181" s="3"/>
+      <c r="E181" s="3"/>
+      <c r="F181" s="3"/>
+      <c r="G181" s="3"/>
+      <c r="H181" s="3"/>
+    </row>
+    <row r="182" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B182" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C182" s="3"/>
+      <c r="D182" s="3"/>
+      <c r="E182" s="3"/>
+      <c r="F182" s="3"/>
+      <c r="G182" s="3"/>
+      <c r="H182" s="3"/>
+    </row>
+    <row r="183" spans="2:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B183" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C183" s="3"/>
+      <c r="D183" s="3"/>
+      <c r="E183" s="3"/>
+      <c r="F183" s="3"/>
+      <c r="G183" s="3"/>
+      <c r="H183" s="3"/>
+    </row>
+    <row r="184" spans="2:8" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B184" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C184" s="1"/>
+      <c r="D184" s="1"/>
+      <c r="E184" s="1"/>
+      <c r="F184" s="1"/>
+      <c r="G184" s="1"/>
+    </row>
+    <row r="187" spans="2:8" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B187" s="28" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="202" spans="2:2" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B202" s="28" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="203" spans="2:2" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B203" s="28" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
+    <mergeCell ref="B183:H183"/>
+    <mergeCell ref="B184:G184"/>
+    <mergeCell ref="B177:H177"/>
+    <mergeCell ref="B179:H179"/>
+    <mergeCell ref="B180:H180"/>
+    <mergeCell ref="B181:H181"/>
+    <mergeCell ref="B182:H182"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B149:I149"/>
-    <mergeCell ref="B150:H150"/>
-    <mergeCell ref="B157:G157"/>
-    <mergeCell ref="B152:H152"/>
-    <mergeCell ref="B153:H153"/>
-    <mergeCell ref="B154:H154"/>
-    <mergeCell ref="B155:H155"/>
-    <mergeCell ref="B156:H156"/>
+    <mergeCell ref="B175:I175"/>
+    <mergeCell ref="B176:H176"/>
   </mergeCells>
   <printOptions headings="1" gridLines="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
